--- a/results/latest.xlsx
+++ b/results/latest.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="638">
   <si>
     <t>Symbol</t>
   </si>
@@ -92,7 +92,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Strict signals — ALL 5 conditions met.  Run: 2026-06-10 05:58</t>
+    <t>Strict signals — ALL 5 conditions met.  Run: 2026-06-10 06:26</t>
   </si>
   <si>
     <t>Score</t>
@@ -119,12 +119,12 @@
     <t>TIINDIA</t>
   </si>
   <si>
+    <t>CANBK</t>
+  </si>
+  <si>
     <t>DEEPAKFERT</t>
   </si>
   <si>
-    <t>CANBK</t>
-  </si>
-  <si>
     <t>SFL</t>
   </si>
   <si>
@@ -227,12 +227,12 @@
     <t>PREMIERENE</t>
   </si>
   <si>
+    <t>JSWENERGY</t>
+  </si>
+  <si>
     <t>FEDERALBNK</t>
   </si>
   <si>
-    <t>JSWENERGY</t>
-  </si>
-  <si>
     <t>COHANCE</t>
   </si>
   <si>
@@ -257,12 +257,12 @@
     <t>TUBE INVESTMENTS OF INDIA LIMITED</t>
   </si>
   <si>
+    <t>CANARA BANK</t>
+  </si>
+  <si>
     <t>DEEPAK FERTILISERS &amp; PETROCHEMICALS</t>
   </si>
   <si>
-    <t>CANARA BANK</t>
-  </si>
-  <si>
     <t>SHEELA FOAM LTD</t>
   </si>
   <si>
@@ -365,12 +365,12 @@
     <t>PREMIER ENERGIES LTD</t>
   </si>
   <si>
+    <t>JSW ENERGY LIMITED</t>
+  </si>
+  <si>
     <t>FEDERAL BANK LTD</t>
   </si>
   <si>
-    <t>JSW ENERGY LIMITED</t>
-  </si>
-  <si>
     <t>COHANCE LIFESCIENCES LIMITED</t>
   </si>
   <si>
@@ -572,18 +572,18 @@
     <t>CIPLA</t>
   </si>
   <si>
+    <t>TVSMOTOR</t>
+  </si>
+  <si>
     <t>PAGEIND</t>
   </si>
   <si>
-    <t>TVSMOTOR</t>
+    <t>CUMMINSIND</t>
   </si>
   <si>
     <t>VOLTAS</t>
   </si>
   <si>
-    <t>CUMMINSIND</t>
-  </si>
-  <si>
     <t>TMPV</t>
   </si>
   <si>
@@ -629,12 +629,12 @@
     <t>SHREECEM</t>
   </si>
   <si>
+    <t>KARURVYSYA</t>
+  </si>
+  <si>
     <t>SUPREMEIND</t>
   </si>
   <si>
-    <t>KARURVYSYA</t>
-  </si>
-  <si>
     <t>CANFINHOME</t>
   </si>
   <si>
@@ -680,15 +680,15 @@
     <t>MUTHOOTFIN</t>
   </si>
   <si>
+    <t>UNOMINDA</t>
+  </si>
+  <si>
+    <t>CHOLAFIN</t>
+  </si>
+  <si>
     <t>ITCHOTELS</t>
   </si>
   <si>
-    <t>UNOMINDA</t>
-  </si>
-  <si>
-    <t>CHOLAFIN</t>
-  </si>
-  <si>
     <t>HDFCLIFE</t>
   </si>
   <si>
@@ -719,12 +719,12 @@
     <t>KOTAKBANK</t>
   </si>
   <si>
+    <t>CRAFTSMAN</t>
+  </si>
+  <si>
     <t>BIOCON</t>
   </si>
   <si>
-    <t>CRAFTSMAN</t>
-  </si>
-  <si>
     <t>ASIANPAINT</t>
   </si>
   <si>
@@ -743,18 +743,18 @@
     <t>ACUTAAS</t>
   </si>
   <si>
+    <t>BHEL</t>
+  </si>
+  <si>
     <t>POWERINDIA</t>
   </si>
   <si>
-    <t>BHEL</t>
+    <t>BSE</t>
   </si>
   <si>
     <t>NEULANDLAB</t>
   </si>
   <si>
-    <t>BSE</t>
-  </si>
-  <si>
     <t>MAXHEALTH</t>
   </si>
   <si>
@@ -767,21 +767,21 @@
     <t>PHOENIXLTD</t>
   </si>
   <si>
+    <t>CGPOWER</t>
+  </si>
+  <si>
     <t>GVT&amp;D</t>
   </si>
   <si>
-    <t>CGPOWER</t>
-  </si>
-  <si>
     <t>HINDZINC</t>
   </si>
   <si>
+    <t>ABB</t>
+  </si>
+  <si>
     <t>RADICO</t>
   </si>
   <si>
-    <t>ABB</t>
-  </si>
-  <si>
     <t>WIPRO</t>
   </si>
   <si>
@@ -797,12 +797,12 @@
     <t>NESTLEIND</t>
   </si>
   <si>
+    <t>COFORGE</t>
+  </si>
+  <si>
     <t>FEDFINA</t>
   </si>
   <si>
-    <t>COFORGE</t>
-  </si>
-  <si>
     <t>TECHM</t>
   </si>
   <si>
@@ -854,18 +854,18 @@
     <t>BAJAJ-AUTO</t>
   </si>
   <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
     <t>BHARTIHEXA</t>
   </si>
   <si>
-    <t>JIOFIN</t>
+    <t>RAMCOCEM</t>
   </si>
   <si>
     <t>OBEROIRLTY</t>
   </si>
   <si>
-    <t>RAMCOCEM</t>
-  </si>
-  <si>
     <t>MANAPPURAM</t>
   </si>
   <si>
@@ -887,6 +887,9 @@
     <t>JKCEMENT</t>
   </si>
   <si>
+    <t>ZFCVINDIA</t>
+  </si>
+  <si>
     <t>GLAXO</t>
   </si>
   <si>
@@ -896,9 +899,6 @@
     <t>DOMS</t>
   </si>
   <si>
-    <t>ZFCVINDIA</t>
-  </si>
-  <si>
     <t>MCX</t>
   </si>
   <si>
@@ -908,12 +908,12 @@
     <t>NMDC</t>
   </si>
   <si>
+    <t>UNITDSPR</t>
+  </si>
+  <si>
     <t>CEATLTD</t>
   </si>
   <si>
-    <t>UNITDSPR</t>
-  </si>
-  <si>
     <t>BAJAJFINSV</t>
   </si>
   <si>
@@ -932,12 +932,12 @@
     <t>BAJFINANCE</t>
   </si>
   <si>
+    <t>NAVINFLUOR</t>
+  </si>
+  <si>
     <t>LTF</t>
   </si>
   <si>
-    <t>NAVINFLUOR</t>
-  </si>
-  <si>
     <t>BRITANNIA</t>
   </si>
   <si>
@@ -962,12 +962,12 @@
     <t>PERSISTENT</t>
   </si>
   <si>
+    <t>GODREJCP</t>
+  </si>
+  <si>
     <t>UPL</t>
   </si>
   <si>
-    <t>GODREJCP</t>
-  </si>
-  <si>
     <t>ELIN</t>
   </si>
   <si>
@@ -989,18 +989,18 @@
     <t>PRESTIGE</t>
   </si>
   <si>
+    <t>BPCL</t>
+  </si>
+  <si>
+    <t>CESC</t>
+  </si>
+  <si>
     <t>HAVELLS</t>
   </si>
   <si>
     <t>STAR</t>
   </si>
   <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>CESC</t>
-  </si>
-  <si>
     <t>INFY</t>
   </si>
   <si>
@@ -1076,36 +1076,36 @@
     <t>POWERGRID</t>
   </si>
   <si>
+    <t>SCHAEFFLER</t>
+  </si>
+  <si>
     <t>RRKABEL</t>
   </si>
   <si>
-    <t>SCHAEFFLER</t>
-  </si>
-  <si>
     <t>ICICIPRULI</t>
   </si>
   <si>
+    <t>INDIASHLTR</t>
+  </si>
+  <si>
     <t>AMBUJACEM</t>
   </si>
   <si>
-    <t>INDIASHLTR</t>
-  </si>
-  <si>
     <t>LTM</t>
   </si>
   <si>
     <t>APLAPOLLO</t>
   </si>
   <si>
+    <t>CHOLAHLDNG</t>
+  </si>
+  <si>
     <t>SBICARD</t>
   </si>
   <si>
     <t>NAUKRI</t>
   </si>
   <si>
-    <t>CHOLAHLDNG</t>
-  </si>
-  <si>
     <t>TATACONSUM</t>
   </si>
   <si>
@@ -1208,18 +1208,18 @@
     <t>CIPLA LTD</t>
   </si>
   <si>
+    <t>TVS MOTOR CO.LTD</t>
+  </si>
+  <si>
     <t>PAGE INDUSTRIES</t>
   </si>
   <si>
-    <t>TVS MOTOR CO.LTD</t>
+    <t>CUMMINS INDIA LTD</t>
   </si>
   <si>
     <t>VOLTAS LTD</t>
   </si>
   <si>
-    <t>CUMMINS INDIA LTD</t>
-  </si>
-  <si>
     <t>TATA MOTORS PASSENGER VEHICLES LIMITED</t>
   </si>
   <si>
@@ -1265,12 +1265,12 @@
     <t>SHREE CEMENT LTD</t>
   </si>
   <si>
+    <t>KARUR VYSYA BANK</t>
+  </si>
+  <si>
     <t>SUPREME INDUSTRIES LTD FV 2</t>
   </si>
   <si>
-    <t>KARUR VYSYA BANK</t>
-  </si>
-  <si>
     <t>CAN FIN HOMES LTD</t>
   </si>
   <si>
@@ -1295,7 +1295,7 @@
     <t>RAINBOW CHILDRENS MEDICARE LIMITED</t>
   </si>
   <si>
-    <t>RELIANCE INDUSTRIES LTD</t>
+    <t>Reliance Industries Limited</t>
   </si>
   <si>
     <t>HINDUSTAN PETROLEUM CORPORATION LIMITED</t>
@@ -1316,15 +1316,15 @@
     <t>MUTHOOT FINANCE LIMITED</t>
   </si>
   <si>
+    <t>UNO MINDA LIMITED</t>
+  </si>
+  <si>
+    <t>CHOLAMANDALAM INVESTMENT &amp; FINANCE COMPANY LIMITED</t>
+  </si>
+  <si>
     <t>ITC HOTELS LTD</t>
   </si>
   <si>
-    <t>UNO MINDA LIMITED</t>
-  </si>
-  <si>
-    <t>CHOLAMANDALAM INVESTMENT &amp; FINANCE COMPANY LIMITED</t>
-  </si>
-  <si>
     <t>HDFC LIFE INSURANCE COMPANY LIMITED</t>
   </si>
   <si>
@@ -1355,12 +1355,12 @@
     <t>KOTAK MAHINDRA BANK LTD</t>
   </si>
   <si>
+    <t>CRAFTSMAN AUTOMATION LTD</t>
+  </si>
+  <si>
     <t>BIOCON LTD</t>
   </si>
   <si>
-    <t>CRAFTSMAN AUTOMATION LTD</t>
-  </si>
-  <si>
     <t>ASIAN PAINTS LTD</t>
   </si>
   <si>
@@ -1379,18 +1379,18 @@
     <t>ACUTAAS CHEMICALS LIMITED</t>
   </si>
   <si>
+    <t>BHARAT HEAVY ELECTRICALS LTD</t>
+  </si>
+  <si>
     <t>HITACHI ENERGY INDIA LTD</t>
   </si>
   <si>
-    <t>BHARAT HEAVY ELECTRICALS LTD</t>
+    <t>BSE LIMITED</t>
   </si>
   <si>
     <t>NEULAND LABORATORIES LIMITED</t>
   </si>
   <si>
-    <t>BSE LIMITED</t>
-  </si>
-  <si>
     <t>MAX HEALTHCARE INSTITUTE LIMITED</t>
   </si>
   <si>
@@ -1403,21 +1403,21 @@
     <t>THE PHOENIX MILLS LIMITED</t>
   </si>
   <si>
+    <t>CG POWER AND INDUSTRIAL SOLUTIONS LIMITED</t>
+  </si>
+  <si>
     <t>GE VERNOVA T&amp;D INDIA LTD</t>
   </si>
   <si>
-    <t>CG POWER AND INDUSTRIAL SOLUTIONS LIMITED</t>
-  </si>
-  <si>
     <t>HINDUSTAN ZINC LTD</t>
   </si>
   <si>
+    <t>ABB INDIA LIMITED</t>
+  </si>
+  <si>
     <t>RADICO KHAITAN LIMITED</t>
   </si>
   <si>
-    <t>ABB INDIA LIMITED</t>
-  </si>
-  <si>
     <t>WIPRO LTD</t>
   </si>
   <si>
@@ -1433,12 +1433,12 @@
     <t>NESTLE INDIA LTD</t>
   </si>
   <si>
+    <t>COFORGE LTD</t>
+  </si>
+  <si>
     <t>FEDBANK FINANCIAL SERVICES LIMITED</t>
   </si>
   <si>
-    <t>COFORGE LTD</t>
-  </si>
-  <si>
     <t>TECH MAHINDRA LTD</t>
   </si>
   <si>
@@ -1490,18 +1490,18 @@
     <t>BAJAJ AUTO LTD</t>
   </si>
   <si>
+    <t>JIO FINANCIAL SERVICES LIMITED</t>
+  </si>
+  <si>
     <t>BHARTI HEXACOM LIMITED</t>
   </si>
   <si>
-    <t>JIO FINANCIAL SERVICES LIMITED</t>
+    <t>THE RAMCO CEMENTS LIMITED</t>
   </si>
   <si>
     <t>OBEROI REALITY LTD</t>
   </si>
   <si>
-    <t>THE RAMCO CEMENTS LIMITED</t>
-  </si>
-  <si>
     <t>MANAPPURAM FINANCE LIMITED</t>
   </si>
   <si>
@@ -1523,6 +1523,9 @@
     <t>JK CEMENT LIMITED</t>
   </si>
   <si>
+    <t>ZF COMMERCIAL VEHICLE CONTROL SYSTEMS INDIA LTD</t>
+  </si>
+  <si>
     <t>GLAXOSMITHKLINE PHARMACEUTICALS LTD</t>
   </si>
   <si>
@@ -1532,9 +1535,6 @@
     <t>DOMS INDUSTRIES LIMITED</t>
   </si>
   <si>
-    <t>ZF COMMERCIAL VEHICLE CONTROL SYSTEMS INDIA LTD</t>
-  </si>
-  <si>
     <t>MULTI COMMODITY EXCHANGE OF (I) LTD. FV 5</t>
   </si>
   <si>
@@ -1544,12 +1544,12 @@
     <t>NATIONAL MINARAL DEVELOPMENT CORPORATION LIMITED</t>
   </si>
   <si>
+    <t>UNITED SPIRITS LIMITED</t>
+  </si>
+  <si>
     <t>CEAT LIMITED</t>
   </si>
   <si>
-    <t>UNITED SPIRITS LIMITED</t>
-  </si>
-  <si>
     <t>BAJAJ FINSERV LIMITED</t>
   </si>
   <si>
@@ -1568,12 +1568,12 @@
     <t>BAJAJ FINANCE LIMITED</t>
   </si>
   <si>
+    <t>NAVIN FLUORINE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
     <t>L&amp;T FINANCE LIMITED</t>
   </si>
   <si>
-    <t>NAVIN FLUORINE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
     <t>BRITANNIA INDUSTRIES LTD</t>
   </si>
   <si>
@@ -1598,12 +1598,12 @@
     <t>PERSISTENT SYSTEMS LIMITED</t>
   </si>
   <si>
+    <t>GODREJ CONSUMER PRODUCTS LTD</t>
+  </si>
+  <si>
     <t>UPL LIMITED</t>
   </si>
   <si>
-    <t>GODREJ CONSUMER PRODUCTS LTD</t>
-  </si>
-  <si>
     <t>ELIN ELECTRONICS LIMITED</t>
   </si>
   <si>
@@ -1625,18 +1625,18 @@
     <t>PRESTIGE ESTATES PROJECTS LIMITED</t>
   </si>
   <si>
+    <t>BHARAT PETROLEUM CORPORATION LTD</t>
+  </si>
+  <si>
+    <t>CESC LTD</t>
+  </si>
+  <si>
     <t>HAVELLS INDIA LTD</t>
   </si>
   <si>
     <t>STRIDES PHARMA SCIENCE LTD</t>
   </si>
   <si>
-    <t>BHARAT PETROLEUM CORPORATION LTD</t>
-  </si>
-  <si>
-    <t>CESC LTD</t>
-  </si>
-  <si>
     <t>INFOSYS LIMITED</t>
   </si>
   <si>
@@ -1712,36 +1712,36 @@
     <t>POWER GRID CORPN. OF INDIA LTD</t>
   </si>
   <si>
+    <t>SCHAEFFLER INDIA LIMITED</t>
+  </si>
+  <si>
     <t>RR KABEL LIMITED</t>
   </si>
   <si>
-    <t>SCHAEFFLER INDIA LIMITED</t>
-  </si>
-  <si>
     <t>ICICI PRUDENTIAL LIFE INSURANCE COMPANY LIMITED</t>
   </si>
   <si>
+    <t>INDIA SHELTER FINANCE CORPORATION LIMITED</t>
+  </si>
+  <si>
     <t>AMBUJA CEMENTS LIMITED</t>
   </si>
   <si>
-    <t>INDIA SHELTER FINANCE CORPORATION LIMITED</t>
-  </si>
-  <si>
     <t>LTIMINDTREE LIMITED</t>
   </si>
   <si>
     <t>APL APOLLO TUBES LIMITED</t>
   </si>
   <si>
+    <t>CHOLAMANDALAM FINANCIAL HOLDINGS LTD</t>
+  </si>
+  <si>
     <t>SBI CARDS AND PAYMENT SERVICES LIMITED</t>
   </si>
   <si>
     <t>INFO EDGE (INDIA) LTD</t>
   </si>
   <si>
-    <t>CHOLAMANDALAM FINANCIAL HOLDINGS LTD</t>
-  </si>
-  <si>
     <t>TATA CONSUMER PRODUCTS LIMITED</t>
   </si>
   <si>
@@ -1886,7 +1886,7 @@
     <t>Stock Breakout Scanner</t>
   </si>
   <si>
-    <t>Run time: 2026-06-10 05:58:55  |  Data as of EOD: 2026-06-09</t>
+    <t>Run time: 2026-06-10 06:26:58  |  Data as of EOD: 2026-06-09</t>
   </si>
   <si>
     <t>Note: 'Current Price' = last completed daily close (EOD), not a live intraday price. Ties exactly to NSE Bhavcopy.</t>
@@ -2881,28 +2881,28 @@
         <v>77</v>
       </c>
       <c r="C8">
-        <v>1518.6</v>
+        <v>137.51</v>
       </c>
       <c r="D8">
-        <v>72.7</v>
+        <v>57.77</v>
       </c>
       <c r="E8">
-        <v>1474.21</v>
+        <v>132.18</v>
       </c>
       <c r="F8">
-        <v>1410.41</v>
+        <v>130.7</v>
       </c>
       <c r="G8">
-        <v>1266</v>
+        <v>136.23</v>
       </c>
       <c r="H8">
-        <v>1242.55</v>
+        <v>142.58</v>
       </c>
       <c r="I8">
-        <v>584139</v>
+        <v>57740162</v>
       </c>
       <c r="J8">
-        <v>318254</v>
+        <v>31317134</v>
       </c>
       <c r="K8">
         <v>1.84</v>
@@ -2917,10 +2917,10 @@
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2931,28 +2931,28 @@
         <v>78</v>
       </c>
       <c r="C9">
-        <v>137.51</v>
+        <v>1518.6</v>
       </c>
       <c r="D9">
-        <v>57.77</v>
+        <v>72.7</v>
       </c>
       <c r="E9">
-        <v>132.18</v>
+        <v>1474.21</v>
       </c>
       <c r="F9">
-        <v>130.7</v>
+        <v>1410.41</v>
       </c>
       <c r="G9">
-        <v>136.23</v>
+        <v>1266</v>
       </c>
       <c r="H9">
-        <v>142.58</v>
+        <v>1242.55</v>
       </c>
       <c r="I9">
-        <v>57740162</v>
+        <v>584139</v>
       </c>
       <c r="J9">
-        <v>31317134</v>
+        <v>318254</v>
       </c>
       <c r="K9">
         <v>1.84</v>
@@ -2967,10 +2967,10 @@
         <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -4681,28 +4681,28 @@
         <v>113</v>
       </c>
       <c r="C44">
-        <v>315.1</v>
+        <v>570.4</v>
       </c>
       <c r="D44">
-        <v>75.48999999999999</v>
+        <v>52.74</v>
       </c>
       <c r="E44">
-        <v>301.18</v>
+        <v>584.52</v>
       </c>
       <c r="F44">
-        <v>297.03</v>
+        <v>576.54</v>
       </c>
       <c r="G44">
-        <v>299.12</v>
+        <v>552.0599999999999</v>
       </c>
       <c r="H44">
-        <v>294.3</v>
+        <v>517.83</v>
       </c>
       <c r="I44">
-        <v>14386417</v>
+        <v>1964709</v>
       </c>
       <c r="J44">
-        <v>31616185</v>
+        <v>4232119</v>
       </c>
       <c r="K44">
         <v>0.46</v>
@@ -4717,10 +4717,10 @@
         <v>3</v>
       </c>
       <c r="O44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P44" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4731,28 +4731,28 @@
         <v>114</v>
       </c>
       <c r="C45">
-        <v>570.4</v>
+        <v>315.1</v>
       </c>
       <c r="D45">
-        <v>52.74</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="E45">
-        <v>584.52</v>
+        <v>301.18</v>
       </c>
       <c r="F45">
-        <v>576.54</v>
+        <v>297.03</v>
       </c>
       <c r="G45">
-        <v>552.0599999999999</v>
+        <v>299.12</v>
       </c>
       <c r="H45">
-        <v>517.83</v>
+        <v>294.3</v>
       </c>
       <c r="I45">
-        <v>1964709</v>
+        <v>14386417</v>
       </c>
       <c r="J45">
-        <v>4232119</v>
+        <v>31616185</v>
       </c>
       <c r="K45">
         <v>0.46</v>
@@ -4767,10 +4767,10 @@
         <v>3</v>
       </c>
       <c r="O45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P45" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -5833,28 +5833,28 @@
         <v>77</v>
       </c>
       <c r="C12">
-        <v>1518.6</v>
+        <v>137.51</v>
       </c>
       <c r="D12">
-        <v>72.7</v>
+        <v>57.77</v>
       </c>
       <c r="E12">
-        <v>1474.21</v>
+        <v>132.18</v>
       </c>
       <c r="F12">
-        <v>1410.41</v>
+        <v>130.7</v>
       </c>
       <c r="G12">
-        <v>1266</v>
+        <v>136.23</v>
       </c>
       <c r="H12">
-        <v>1242.55</v>
+        <v>142.58</v>
       </c>
       <c r="I12">
-        <v>584139</v>
+        <v>57740162</v>
       </c>
       <c r="J12">
-        <v>318254</v>
+        <v>31317134</v>
       </c>
       <c r="K12">
         <v>1.84</v>
@@ -5866,22 +5866,22 @@
         <v>21</v>
       </c>
       <c r="N12">
-        <v>1440.04</v>
+        <v>130.78</v>
       </c>
       <c r="O12">
-        <v>54.59</v>
+        <v>4.01</v>
       </c>
       <c r="P12">
-        <v>1436.72</v>
+        <v>131.49</v>
       </c>
       <c r="Q12">
-        <v>1682.37</v>
+        <v>149.55</v>
       </c>
       <c r="R12">
-        <v>5.39</v>
+        <v>4.38</v>
       </c>
       <c r="S12">
-        <v>10.78</v>
+        <v>8.75</v>
       </c>
       <c r="T12" t="s">
         <v>155</v>
@@ -5890,10 +5890,10 @@
         <v>4</v>
       </c>
       <c r="V12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -5904,28 +5904,28 @@
         <v>78</v>
       </c>
       <c r="C13">
-        <v>137.51</v>
+        <v>1518.6</v>
       </c>
       <c r="D13">
-        <v>57.77</v>
+        <v>72.7</v>
       </c>
       <c r="E13">
-        <v>132.18</v>
+        <v>1474.21</v>
       </c>
       <c r="F13">
-        <v>130.7</v>
+        <v>1410.41</v>
       </c>
       <c r="G13">
-        <v>136.23</v>
+        <v>1266</v>
       </c>
       <c r="H13">
-        <v>142.58</v>
+        <v>1242.55</v>
       </c>
       <c r="I13">
-        <v>57740162</v>
+        <v>584139</v>
       </c>
       <c r="J13">
-        <v>31317134</v>
+        <v>318254</v>
       </c>
       <c r="K13">
         <v>1.84</v>
@@ -5937,22 +5937,22 @@
         <v>21</v>
       </c>
       <c r="N13">
-        <v>130.78</v>
+        <v>1440.04</v>
       </c>
       <c r="O13">
-        <v>4.01</v>
+        <v>54.59</v>
       </c>
       <c r="P13">
-        <v>131.49</v>
+        <v>1436.72</v>
       </c>
       <c r="Q13">
-        <v>149.55</v>
+        <v>1682.37</v>
       </c>
       <c r="R13">
-        <v>4.38</v>
+        <v>5.39</v>
       </c>
       <c r="S13">
-        <v>8.75</v>
+        <v>10.78</v>
       </c>
       <c r="T13" t="s">
         <v>155</v>
@@ -5961,10 +5961,10 @@
         <v>4</v>
       </c>
       <c r="V13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -8389,28 +8389,28 @@
         <v>113</v>
       </c>
       <c r="C48">
-        <v>315.1</v>
+        <v>570.4</v>
       </c>
       <c r="D48">
-        <v>75.48999999999999</v>
+        <v>52.74</v>
       </c>
       <c r="E48">
-        <v>301.18</v>
+        <v>584.52</v>
       </c>
       <c r="F48">
-        <v>297.03</v>
+        <v>576.54</v>
       </c>
       <c r="G48">
-        <v>299.12</v>
+        <v>552.0599999999999</v>
       </c>
       <c r="H48">
-        <v>294.3</v>
+        <v>517.83</v>
       </c>
       <c r="I48">
-        <v>14386417</v>
+        <v>1964709</v>
       </c>
       <c r="J48">
-        <v>31616185</v>
+        <v>4232119</v>
       </c>
       <c r="K48">
         <v>0.46</v>
@@ -8422,22 +8422,22 @@
         <v>21</v>
       </c>
       <c r="N48">
-        <v>301.47</v>
+        <v>556.72</v>
       </c>
       <c r="O48">
-        <v>7.82</v>
+        <v>18.45</v>
       </c>
       <c r="P48">
-        <v>303.36</v>
+        <v>542.72</v>
       </c>
       <c r="Q48">
-        <v>338.57</v>
+        <v>625.76</v>
       </c>
       <c r="R48">
-        <v>3.72</v>
+        <v>4.85</v>
       </c>
       <c r="S48">
-        <v>7.45</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="T48" t="s">
         <v>155</v>
@@ -8446,10 +8446,10 @@
         <v>3</v>
       </c>
       <c r="V48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W48" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -8460,28 +8460,28 @@
         <v>114</v>
       </c>
       <c r="C49">
-        <v>570.4</v>
+        <v>315.1</v>
       </c>
       <c r="D49">
-        <v>52.74</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="E49">
-        <v>584.52</v>
+        <v>301.18</v>
       </c>
       <c r="F49">
-        <v>576.54</v>
+        <v>297.03</v>
       </c>
       <c r="G49">
-        <v>552.0599999999999</v>
+        <v>299.12</v>
       </c>
       <c r="H49">
-        <v>517.83</v>
+        <v>294.3</v>
       </c>
       <c r="I49">
-        <v>1964709</v>
+        <v>14386417</v>
       </c>
       <c r="J49">
-        <v>4232119</v>
+        <v>31616185</v>
       </c>
       <c r="K49">
         <v>0.46</v>
@@ -8493,22 +8493,22 @@
         <v>21</v>
       </c>
       <c r="N49">
-        <v>556.72</v>
+        <v>301.47</v>
       </c>
       <c r="O49">
-        <v>18.45</v>
+        <v>7.82</v>
       </c>
       <c r="P49">
-        <v>542.72</v>
+        <v>303.36</v>
       </c>
       <c r="Q49">
-        <v>625.76</v>
+        <v>338.57</v>
       </c>
       <c r="R49">
-        <v>4.85</v>
+        <v>3.72</v>
       </c>
       <c r="S49">
-        <v>9.710000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="T49" t="s">
         <v>155</v>
@@ -8517,10 +8517,10 @@
         <v>3</v>
       </c>
       <c r="V49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W49" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -10448,55 +10448,55 @@
         <v>394</v>
       </c>
       <c r="C77">
-        <v>38905</v>
+        <v>3358</v>
       </c>
       <c r="D77">
-        <v>60.04</v>
+        <v>44.19</v>
       </c>
       <c r="E77">
-        <v>38618.84</v>
+        <v>3331.77</v>
       </c>
       <c r="F77">
-        <v>38185.39</v>
+        <v>3387.62</v>
       </c>
       <c r="G77">
-        <v>35928.75</v>
+        <v>3527.7</v>
       </c>
       <c r="H77">
-        <v>35086.54</v>
+        <v>3691.69</v>
       </c>
       <c r="I77">
-        <v>18287</v>
+        <v>797346</v>
       </c>
       <c r="J77">
-        <v>25453</v>
+        <v>1113376</v>
       </c>
       <c r="K77">
         <v>0.72</v>
       </c>
       <c r="L77" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="M77" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="N77">
-        <v>36081.82</v>
+        <v>3292.42</v>
       </c>
       <c r="O77">
-        <v>1020.6</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P77">
-        <v>37374.1</v>
+        <v>3222.1</v>
       </c>
       <c r="Q77">
-        <v>41966.8</v>
+        <v>3629.81</v>
       </c>
       <c r="R77">
-        <v>3.93</v>
+        <v>4.05</v>
       </c>
       <c r="S77">
-        <v>7.87</v>
+        <v>8.09</v>
       </c>
       <c r="T77" t="s">
         <v>155</v>
@@ -10505,10 +10505,10 @@
         <v>2</v>
       </c>
       <c r="V77" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="W77" t="s">
-        <v>600</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:23">
@@ -10519,55 +10519,55 @@
         <v>395</v>
       </c>
       <c r="C78">
-        <v>3358</v>
+        <v>38905</v>
       </c>
       <c r="D78">
-        <v>44.19</v>
+        <v>60.04</v>
       </c>
       <c r="E78">
-        <v>3331.77</v>
+        <v>38618.84</v>
       </c>
       <c r="F78">
-        <v>3387.62</v>
+        <v>38185.39</v>
       </c>
       <c r="G78">
-        <v>3527.7</v>
+        <v>35928.75</v>
       </c>
       <c r="H78">
-        <v>3691.69</v>
+        <v>35086.54</v>
       </c>
       <c r="I78">
-        <v>797346</v>
+        <v>18287</v>
       </c>
       <c r="J78">
-        <v>1113376</v>
+        <v>25453</v>
       </c>
       <c r="K78">
         <v>0.72</v>
       </c>
       <c r="L78" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="M78" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="N78">
-        <v>3292.42</v>
+        <v>36081.82</v>
       </c>
       <c r="O78">
-        <v>90.59999999999999</v>
+        <v>1020.6</v>
       </c>
       <c r="P78">
-        <v>3222.1</v>
+        <v>37374.1</v>
       </c>
       <c r="Q78">
-        <v>3629.81</v>
+        <v>41966.8</v>
       </c>
       <c r="R78">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="S78">
-        <v>8.09</v>
+        <v>7.87</v>
       </c>
       <c r="T78" t="s">
         <v>155</v>
@@ -10576,10 +10576,10 @@
         <v>2</v>
       </c>
       <c r="V78" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="W78" t="s">
-        <v>139</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -10590,28 +10590,28 @@
         <v>396</v>
       </c>
       <c r="C79">
-        <v>1304.4</v>
+        <v>5625.5</v>
       </c>
       <c r="D79">
-        <v>51.43</v>
+        <v>54.86</v>
       </c>
       <c r="E79">
-        <v>1256.93</v>
+        <v>5771.31</v>
       </c>
       <c r="F79">
-        <v>1276.49</v>
+        <v>5695.51</v>
       </c>
       <c r="G79">
-        <v>1321.89</v>
+        <v>5513.53</v>
       </c>
       <c r="H79">
-        <v>1343.03</v>
+        <v>5218.6</v>
       </c>
       <c r="I79">
-        <v>883516</v>
+        <v>485174</v>
       </c>
       <c r="J79">
-        <v>1300516</v>
+        <v>710027</v>
       </c>
       <c r="K79">
         <v>0.68</v>
@@ -10623,22 +10623,22 @@
         <v>118</v>
       </c>
       <c r="N79">
-        <v>1224.3</v>
+        <v>5430.17</v>
       </c>
       <c r="O79">
-        <v>44.36</v>
+        <v>166.7</v>
       </c>
       <c r="P79">
-        <v>1237.86</v>
+        <v>5375.46</v>
       </c>
       <c r="Q79">
-        <v>1437.49</v>
+        <v>6125.59</v>
       </c>
       <c r="R79">
-        <v>5.1</v>
+        <v>4.44</v>
       </c>
       <c r="S79">
-        <v>10.2</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="T79" t="s">
         <v>155</v>
@@ -10661,28 +10661,28 @@
         <v>397</v>
       </c>
       <c r="C80">
-        <v>5625.5</v>
+        <v>1304.4</v>
       </c>
       <c r="D80">
-        <v>54.86</v>
+        <v>51.43</v>
       </c>
       <c r="E80">
-        <v>5771.31</v>
+        <v>1256.93</v>
       </c>
       <c r="F80">
-        <v>5695.51</v>
+        <v>1276.49</v>
       </c>
       <c r="G80">
-        <v>5513.53</v>
+        <v>1321.89</v>
       </c>
       <c r="H80">
-        <v>5218.6</v>
+        <v>1343.03</v>
       </c>
       <c r="I80">
-        <v>485174</v>
+        <v>883516</v>
       </c>
       <c r="J80">
-        <v>710027</v>
+        <v>1300516</v>
       </c>
       <c r="K80">
         <v>0.68</v>
@@ -10694,22 +10694,22 @@
         <v>118</v>
       </c>
       <c r="N80">
-        <v>5430.17</v>
+        <v>1224.3</v>
       </c>
       <c r="O80">
-        <v>166.7</v>
+        <v>44.36</v>
       </c>
       <c r="P80">
-        <v>5375.46</v>
+        <v>1237.86</v>
       </c>
       <c r="Q80">
-        <v>6125.59</v>
+        <v>1437.49</v>
       </c>
       <c r="R80">
-        <v>4.44</v>
+        <v>5.1</v>
       </c>
       <c r="S80">
-        <v>8.890000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="T80" t="s">
         <v>155</v>
@@ -11797,28 +11797,28 @@
         <v>413</v>
       </c>
       <c r="C96">
-        <v>3499.7</v>
+        <v>285.6</v>
       </c>
       <c r="D96">
-        <v>42.6</v>
+        <v>46.77</v>
       </c>
       <c r="E96">
-        <v>3533.76</v>
+        <v>286</v>
       </c>
       <c r="F96">
-        <v>3553.04</v>
+        <v>290.69</v>
       </c>
       <c r="G96">
-        <v>3577.98</v>
+        <v>300.13</v>
       </c>
       <c r="H96">
-        <v>3521.61</v>
+        <v>301.14</v>
       </c>
       <c r="I96">
-        <v>260175</v>
+        <v>3920864</v>
       </c>
       <c r="J96">
-        <v>148636</v>
+        <v>2239211</v>
       </c>
       <c r="K96">
         <v>1.75</v>
@@ -11830,22 +11830,22 @@
         <v>118</v>
       </c>
       <c r="N96">
-        <v>3665.65</v>
+        <v>311.27</v>
       </c>
       <c r="O96">
-        <v>94.34999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="P96">
-        <v>3358.18</v>
+        <v>271.62</v>
       </c>
       <c r="Q96">
-        <v>3782.74</v>
+        <v>313.56</v>
       </c>
       <c r="R96">
-        <v>4.04</v>
+        <v>4.89</v>
       </c>
       <c r="S96">
-        <v>8.09</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="T96" t="s">
         <v>155</v>
@@ -11857,7 +11857,7 @@
         <v>589</v>
       </c>
       <c r="W96" t="s">
-        <v>602</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:23">
@@ -11868,28 +11868,28 @@
         <v>414</v>
       </c>
       <c r="C97">
-        <v>285.6</v>
+        <v>3499.7</v>
       </c>
       <c r="D97">
-        <v>46.77</v>
+        <v>42.6</v>
       </c>
       <c r="E97">
-        <v>286</v>
+        <v>3533.76</v>
       </c>
       <c r="F97">
-        <v>290.69</v>
+        <v>3553.04</v>
       </c>
       <c r="G97">
-        <v>300.13</v>
+        <v>3577.98</v>
       </c>
       <c r="H97">
-        <v>301.14</v>
+        <v>3521.61</v>
       </c>
       <c r="I97">
-        <v>3920864</v>
+        <v>260175</v>
       </c>
       <c r="J97">
-        <v>2239211</v>
+        <v>148636</v>
       </c>
       <c r="K97">
         <v>1.75</v>
@@ -11901,22 +11901,22 @@
         <v>118</v>
       </c>
       <c r="N97">
-        <v>311.27</v>
+        <v>3665.65</v>
       </c>
       <c r="O97">
-        <v>9.32</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="P97">
-        <v>271.62</v>
+        <v>3358.18</v>
       </c>
       <c r="Q97">
-        <v>313.56</v>
+        <v>3782.74</v>
       </c>
       <c r="R97">
-        <v>4.89</v>
+        <v>4.04</v>
       </c>
       <c r="S97">
-        <v>9.789999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="T97" t="s">
         <v>155</v>
@@ -11928,7 +11928,7 @@
         <v>589</v>
       </c>
       <c r="W97" t="s">
-        <v>128</v>
+        <v>602</v>
       </c>
     </row>
     <row r="98" spans="1:23">
@@ -12566,9 +12566,6 @@
       <c r="V106" t="s">
         <v>589</v>
       </c>
-      <c r="W106" t="s">
-        <v>605</v>
-      </c>
     </row>
     <row r="107" spans="1:23">
       <c r="A107" t="s">
@@ -13004,28 +13001,28 @@
         <v>430</v>
       </c>
       <c r="C113">
-        <v>150.87</v>
+        <v>1094</v>
       </c>
       <c r="D113">
-        <v>40.7</v>
+        <v>49.1</v>
       </c>
       <c r="E113">
-        <v>152.35</v>
+        <v>1085.86</v>
       </c>
       <c r="F113">
-        <v>150.8</v>
+        <v>1085.21</v>
       </c>
       <c r="G113">
-        <v>149.26</v>
+        <v>1093.79</v>
       </c>
       <c r="H113">
-        <v>163.79</v>
+        <v>1151.21</v>
       </c>
       <c r="I113">
-        <v>2895360</v>
+        <v>822653</v>
       </c>
       <c r="J113">
-        <v>2630817</v>
+        <v>750756</v>
       </c>
       <c r="K113">
         <v>1.1</v>
@@ -13037,22 +13034,22 @@
         <v>118</v>
       </c>
       <c r="N113">
-        <v>161.1</v>
+        <v>1164.05</v>
       </c>
       <c r="O113">
-        <v>3.74</v>
+        <v>36.3</v>
       </c>
       <c r="P113">
-        <v>145.25</v>
+        <v>1039.55</v>
       </c>
       <c r="Q113">
-        <v>162.1</v>
+        <v>1202.91</v>
       </c>
       <c r="R113">
-        <v>3.72</v>
+        <v>4.98</v>
       </c>
       <c r="S113">
-        <v>7.44</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="T113" t="s">
         <v>155</v>
@@ -13064,7 +13061,7 @@
         <v>589</v>
       </c>
       <c r="W113" t="s">
-        <v>599</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:23">
@@ -13075,28 +13072,28 @@
         <v>431</v>
       </c>
       <c r="C114">
-        <v>1094</v>
+        <v>1495.4</v>
       </c>
       <c r="D114">
-        <v>49.1</v>
+        <v>44.71</v>
       </c>
       <c r="E114">
-        <v>1085.86</v>
+        <v>1495.62</v>
       </c>
       <c r="F114">
-        <v>1085.21</v>
+        <v>1515.58</v>
       </c>
       <c r="G114">
-        <v>1093.79</v>
+        <v>1541.21</v>
       </c>
       <c r="H114">
-        <v>1151.21</v>
+        <v>1604.7</v>
       </c>
       <c r="I114">
-        <v>822653</v>
+        <v>1430472</v>
       </c>
       <c r="J114">
-        <v>750756</v>
+        <v>1299851</v>
       </c>
       <c r="K114">
         <v>1.1</v>
@@ -13108,22 +13105,22 @@
         <v>118</v>
       </c>
       <c r="N114">
-        <v>1164.05</v>
+        <v>1714.46</v>
       </c>
       <c r="O114">
-        <v>36.3</v>
+        <v>49.04</v>
       </c>
       <c r="P114">
-        <v>1039.55</v>
+        <v>1421.83</v>
       </c>
       <c r="Q114">
-        <v>1202.91</v>
+        <v>1642.53</v>
       </c>
       <c r="R114">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="S114">
-        <v>9.960000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="T114" t="s">
         <v>155</v>
@@ -13135,7 +13132,7 @@
         <v>589</v>
       </c>
       <c r="W114" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:23">
@@ -13146,28 +13143,28 @@
         <v>432</v>
       </c>
       <c r="C115">
-        <v>1495.4</v>
+        <v>150.87</v>
       </c>
       <c r="D115">
-        <v>44.71</v>
+        <v>40.7</v>
       </c>
       <c r="E115">
-        <v>1495.62</v>
+        <v>152.35</v>
       </c>
       <c r="F115">
-        <v>1515.58</v>
+        <v>150.8</v>
       </c>
       <c r="G115">
-        <v>1541.21</v>
+        <v>149.26</v>
       </c>
       <c r="H115">
-        <v>1604.7</v>
+        <v>163.79</v>
       </c>
       <c r="I115">
-        <v>1430472</v>
+        <v>2895360</v>
       </c>
       <c r="J115">
-        <v>1299851</v>
+        <v>2630817</v>
       </c>
       <c r="K115">
         <v>1.1</v>
@@ -13179,22 +13176,22 @@
         <v>118</v>
       </c>
       <c r="N115">
-        <v>1714.46</v>
+        <v>161.1</v>
       </c>
       <c r="O115">
-        <v>49.04</v>
+        <v>3.74</v>
       </c>
       <c r="P115">
-        <v>1421.83</v>
+        <v>145.25</v>
       </c>
       <c r="Q115">
-        <v>1642.53</v>
+        <v>162.1</v>
       </c>
       <c r="R115">
-        <v>4.92</v>
+        <v>3.72</v>
       </c>
       <c r="S115">
-        <v>9.84</v>
+        <v>7.44</v>
       </c>
       <c r="T115" t="s">
         <v>155</v>
@@ -13206,7 +13203,7 @@
         <v>589</v>
       </c>
       <c r="W115" t="s">
-        <v>128</v>
+        <v>599</v>
       </c>
     </row>
     <row r="116" spans="1:23">
@@ -13927,28 +13924,28 @@
         <v>443</v>
       </c>
       <c r="C126">
-        <v>416.35</v>
+        <v>9126.5</v>
       </c>
       <c r="D126">
-        <v>55.24</v>
+        <v>64.39</v>
       </c>
       <c r="E126">
-        <v>425.63</v>
+        <v>9128.530000000001</v>
       </c>
       <c r="F126">
-        <v>415.98</v>
+        <v>8833.610000000001</v>
       </c>
       <c r="G126">
-        <v>401.59</v>
+        <v>8505.940000000001</v>
       </c>
       <c r="H126">
-        <v>393.99</v>
+        <v>8262.129999999999</v>
       </c>
       <c r="I126">
-        <v>3205041</v>
+        <v>66943</v>
       </c>
       <c r="J126">
-        <v>3383824</v>
+        <v>70355</v>
       </c>
       <c r="K126">
         <v>0.95</v>
@@ -13960,22 +13957,22 @@
         <v>118</v>
       </c>
       <c r="N126">
-        <v>335.83</v>
+        <v>9230.84</v>
       </c>
       <c r="O126">
-        <v>10.72</v>
+        <v>331.21</v>
       </c>
       <c r="P126">
-        <v>400.27</v>
+        <v>8629.690000000001</v>
       </c>
       <c r="Q126">
-        <v>448.51</v>
+        <v>10120.12</v>
       </c>
       <c r="R126">
-        <v>3.86</v>
+        <v>5.44</v>
       </c>
       <c r="S126">
-        <v>7.72</v>
+        <v>10.89</v>
       </c>
       <c r="T126" t="s">
         <v>155</v>
@@ -13987,7 +13984,7 @@
         <v>591</v>
       </c>
       <c r="W126" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="127" spans="1:23">
@@ -13998,28 +13995,28 @@
         <v>444</v>
       </c>
       <c r="C127">
-        <v>9126.5</v>
+        <v>416.35</v>
       </c>
       <c r="D127">
-        <v>64.39</v>
+        <v>55.24</v>
       </c>
       <c r="E127">
-        <v>9128.530000000001</v>
+        <v>425.63</v>
       </c>
       <c r="F127">
-        <v>8833.610000000001</v>
+        <v>415.98</v>
       </c>
       <c r="G127">
-        <v>8505.940000000001</v>
+        <v>401.59</v>
       </c>
       <c r="H127">
-        <v>8262.129999999999</v>
+        <v>393.99</v>
       </c>
       <c r="I127">
-        <v>66943</v>
+        <v>3205041</v>
       </c>
       <c r="J127">
-        <v>70355</v>
+        <v>3383824</v>
       </c>
       <c r="K127">
         <v>0.95</v>
@@ -14031,22 +14028,22 @@
         <v>118</v>
       </c>
       <c r="N127">
-        <v>9230.84</v>
+        <v>335.83</v>
       </c>
       <c r="O127">
-        <v>331.21</v>
+        <v>10.72</v>
       </c>
       <c r="P127">
-        <v>8629.690000000001</v>
+        <v>400.27</v>
       </c>
       <c r="Q127">
-        <v>10120.12</v>
+        <v>448.51</v>
       </c>
       <c r="R127">
-        <v>5.44</v>
+        <v>3.86</v>
       </c>
       <c r="S127">
-        <v>10.89</v>
+        <v>7.72</v>
       </c>
       <c r="T127" t="s">
         <v>155</v>
@@ -14058,7 +14055,7 @@
         <v>591</v>
       </c>
       <c r="W127" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="128" spans="1:23">
@@ -14495,28 +14492,28 @@
         <v>451</v>
       </c>
       <c r="C134">
-        <v>34610</v>
+        <v>396.55</v>
       </c>
       <c r="D134">
-        <v>50.27</v>
+        <v>53.75</v>
       </c>
       <c r="E134">
-        <v>36667.98</v>
+        <v>411.46</v>
       </c>
       <c r="F134">
-        <v>36787.67</v>
+        <v>412.86</v>
       </c>
       <c r="G134">
-        <v>34346.81</v>
+        <v>379.43</v>
       </c>
       <c r="H134">
-        <v>30595.84</v>
+        <v>337.86</v>
       </c>
       <c r="I134">
-        <v>205184</v>
+        <v>9498965</v>
       </c>
       <c r="J134">
-        <v>250018</v>
+        <v>11612169</v>
       </c>
       <c r="K134">
         <v>0.82</v>
@@ -14528,22 +14525,22 @@
         <v>118</v>
       </c>
       <c r="N134">
-        <v>23690.91</v>
+        <v>249.8</v>
       </c>
       <c r="O134">
-        <v>1434.93</v>
+        <v>13.44</v>
       </c>
       <c r="P134">
-        <v>32457.6</v>
+        <v>376.4</v>
       </c>
       <c r="Q134">
-        <v>38914.8</v>
+        <v>436.86</v>
       </c>
       <c r="R134">
-        <v>6.22</v>
+        <v>5.08</v>
       </c>
       <c r="S134">
-        <v>12.44</v>
+        <v>10.16</v>
       </c>
       <c r="T134" t="s">
         <v>155</v>
@@ -14555,7 +14552,7 @@
         <v>591</v>
       </c>
       <c r="W134" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135" spans="1:23">
@@ -14566,28 +14563,28 @@
         <v>452</v>
       </c>
       <c r="C135">
-        <v>396.55</v>
+        <v>34610</v>
       </c>
       <c r="D135">
-        <v>53.75</v>
+        <v>50.27</v>
       </c>
       <c r="E135">
-        <v>411.46</v>
+        <v>36667.98</v>
       </c>
       <c r="F135">
-        <v>412.86</v>
+        <v>36787.67</v>
       </c>
       <c r="G135">
-        <v>379.43</v>
+        <v>34346.81</v>
       </c>
       <c r="H135">
-        <v>337.86</v>
+        <v>30595.84</v>
       </c>
       <c r="I135">
-        <v>9498965</v>
+        <v>205184</v>
       </c>
       <c r="J135">
-        <v>11612169</v>
+        <v>250018</v>
       </c>
       <c r="K135">
         <v>0.82</v>
@@ -14599,22 +14596,22 @@
         <v>118</v>
       </c>
       <c r="N135">
-        <v>249.8</v>
+        <v>23690.91</v>
       </c>
       <c r="O135">
-        <v>13.44</v>
+        <v>1434.93</v>
       </c>
       <c r="P135">
-        <v>376.4</v>
+        <v>32457.6</v>
       </c>
       <c r="Q135">
-        <v>436.86</v>
+        <v>38914.8</v>
       </c>
       <c r="R135">
-        <v>5.08</v>
+        <v>6.22</v>
       </c>
       <c r="S135">
-        <v>10.16</v>
+        <v>12.44</v>
       </c>
       <c r="T135" t="s">
         <v>155</v>
@@ -14626,7 +14623,7 @@
         <v>591</v>
       </c>
       <c r="W135" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="136" spans="1:23">
@@ -14637,28 +14634,28 @@
         <v>453</v>
       </c>
       <c r="C136">
-        <v>17188</v>
+        <v>3996.3</v>
       </c>
       <c r="D136">
-        <v>61.78</v>
+        <v>52.34</v>
       </c>
       <c r="E136">
-        <v>17264.81</v>
+        <v>4118.03</v>
       </c>
       <c r="F136">
-        <v>17002.44</v>
+        <v>4161.44</v>
       </c>
       <c r="G136">
-        <v>15953.03</v>
+        <v>3917.9</v>
       </c>
       <c r="H136">
-        <v>15645.4</v>
+        <v>3635.03</v>
       </c>
       <c r="I136">
-        <v>30364</v>
+        <v>3318707</v>
       </c>
       <c r="J136">
-        <v>38124</v>
+        <v>4170054</v>
       </c>
       <c r="K136">
         <v>0.8</v>
@@ -14670,22 +14667,22 @@
         <v>118</v>
       </c>
       <c r="N136">
-        <v>17397.38</v>
+        <v>2509.42</v>
       </c>
       <c r="O136">
-        <v>567.98</v>
+        <v>142.68</v>
       </c>
       <c r="P136">
-        <v>16336.03</v>
+        <v>3782.28</v>
       </c>
       <c r="Q136">
-        <v>18891.95</v>
+        <v>4424.34</v>
       </c>
       <c r="R136">
-        <v>4.96</v>
+        <v>5.36</v>
       </c>
       <c r="S136">
-        <v>9.91</v>
+        <v>10.71</v>
       </c>
       <c r="T136" t="s">
         <v>155</v>
@@ -14697,7 +14694,7 @@
         <v>591</v>
       </c>
       <c r="W136" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:23">
@@ -14708,28 +14705,28 @@
         <v>454</v>
       </c>
       <c r="C137">
-        <v>3996.3</v>
+        <v>17188</v>
       </c>
       <c r="D137">
-        <v>52.34</v>
+        <v>61.78</v>
       </c>
       <c r="E137">
-        <v>4118.03</v>
+        <v>17264.81</v>
       </c>
       <c r="F137">
-        <v>4161.44</v>
+        <v>17002.44</v>
       </c>
       <c r="G137">
-        <v>3917.9</v>
+        <v>15953.03</v>
       </c>
       <c r="H137">
-        <v>3635.03</v>
+        <v>15645.4</v>
       </c>
       <c r="I137">
-        <v>3318707</v>
+        <v>30364</v>
       </c>
       <c r="J137">
-        <v>4170054</v>
+        <v>38124</v>
       </c>
       <c r="K137">
         <v>0.8</v>
@@ -14741,22 +14738,22 @@
         <v>118</v>
       </c>
       <c r="N137">
-        <v>2509.42</v>
+        <v>17397.38</v>
       </c>
       <c r="O137">
-        <v>142.68</v>
+        <v>567.98</v>
       </c>
       <c r="P137">
-        <v>3782.28</v>
+        <v>16336.03</v>
       </c>
       <c r="Q137">
-        <v>4424.34</v>
+        <v>18891.95</v>
       </c>
       <c r="R137">
-        <v>5.36</v>
+        <v>4.96</v>
       </c>
       <c r="S137">
-        <v>10.71</v>
+        <v>9.91</v>
       </c>
       <c r="T137" t="s">
         <v>155</v>
@@ -14768,7 +14765,7 @@
         <v>591</v>
       </c>
       <c r="W137" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138" spans="1:23">
@@ -15063,28 +15060,28 @@
         <v>459</v>
       </c>
       <c r="C142">
-        <v>4931</v>
+        <v>911.2</v>
       </c>
       <c r="D142">
-        <v>56.34</v>
+        <v>59.2</v>
       </c>
       <c r="E142">
-        <v>5011.81</v>
+        <v>927.96</v>
       </c>
       <c r="F142">
-        <v>4956.6</v>
+        <v>907.7</v>
       </c>
       <c r="G142">
-        <v>4740.62</v>
+        <v>850.12</v>
       </c>
       <c r="H142">
-        <v>4388.75</v>
+        <v>787.46</v>
       </c>
       <c r="I142">
-        <v>747212</v>
+        <v>3404934</v>
       </c>
       <c r="J142">
-        <v>1112819</v>
+        <v>5058376</v>
       </c>
       <c r="K142">
         <v>0.67</v>
@@ -15095,23 +15092,20 @@
       <c r="M142" t="s">
         <v>118</v>
       </c>
-      <c r="N142">
-        <v>5093.3</v>
-      </c>
       <c r="O142">
-        <v>229.23</v>
+        <v>28.3</v>
       </c>
       <c r="P142">
-        <v>4587.16</v>
+        <v>868.74</v>
       </c>
       <c r="Q142">
-        <v>5618.68</v>
+        <v>996.11</v>
       </c>
       <c r="R142">
-        <v>6.97</v>
+        <v>4.66</v>
       </c>
       <c r="S142">
-        <v>13.95</v>
+        <v>9.32</v>
       </c>
       <c r="T142" t="s">
         <v>155</v>
@@ -15134,28 +15128,28 @@
         <v>460</v>
       </c>
       <c r="C143">
-        <v>911.2</v>
+        <v>4931</v>
       </c>
       <c r="D143">
-        <v>59.2</v>
+        <v>56.34</v>
       </c>
       <c r="E143">
-        <v>927.96</v>
+        <v>5011.81</v>
       </c>
       <c r="F143">
-        <v>907.7</v>
+        <v>4956.6</v>
       </c>
       <c r="G143">
-        <v>850.12</v>
+        <v>4740.62</v>
       </c>
       <c r="H143">
-        <v>787.46</v>
+        <v>4388.75</v>
       </c>
       <c r="I143">
-        <v>3404934</v>
+        <v>747212</v>
       </c>
       <c r="J143">
-        <v>5058376</v>
+        <v>1112819</v>
       </c>
       <c r="K143">
         <v>0.67</v>
@@ -15166,20 +15160,23 @@
       <c r="M143" t="s">
         <v>118</v>
       </c>
+      <c r="N143">
+        <v>5093.3</v>
+      </c>
       <c r="O143">
-        <v>28.3</v>
+        <v>229.23</v>
       </c>
       <c r="P143">
-        <v>868.74</v>
+        <v>4587.16</v>
       </c>
       <c r="Q143">
-        <v>996.11</v>
+        <v>5618.68</v>
       </c>
       <c r="R143">
-        <v>4.66</v>
+        <v>6.97</v>
       </c>
       <c r="S143">
-        <v>9.32</v>
+        <v>13.95</v>
       </c>
       <c r="T143" t="s">
         <v>155</v>
@@ -15273,28 +15270,28 @@
         <v>462</v>
       </c>
       <c r="C145">
-        <v>3500.7</v>
+        <v>6931</v>
       </c>
       <c r="D145">
-        <v>56.68</v>
+        <v>50.27</v>
       </c>
       <c r="E145">
-        <v>3550.63</v>
+        <v>7061.74</v>
       </c>
       <c r="F145">
-        <v>3537.49</v>
+        <v>7136.81</v>
       </c>
       <c r="G145">
-        <v>3359.84</v>
+        <v>6986.95</v>
       </c>
       <c r="H145">
-        <v>3288.45</v>
+        <v>6338.76</v>
       </c>
       <c r="I145">
-        <v>162504</v>
+        <v>254364</v>
       </c>
       <c r="J145">
-        <v>254310</v>
+        <v>400417</v>
       </c>
       <c r="K145">
         <v>0.64</v>
@@ -15306,22 +15303,22 @@
         <v>118</v>
       </c>
       <c r="N145">
-        <v>3595</v>
+        <v>7279.05</v>
       </c>
       <c r="O145">
-        <v>94.75</v>
+        <v>203.24</v>
       </c>
       <c r="P145">
-        <v>3358.57</v>
+        <v>6626.14</v>
       </c>
       <c r="Q145">
-        <v>3784.95</v>
+        <v>7540.71</v>
       </c>
       <c r="R145">
-        <v>4.06</v>
+        <v>4.4</v>
       </c>
       <c r="S145">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T145" t="s">
         <v>155</v>
@@ -15333,7 +15330,7 @@
         <v>591</v>
       </c>
       <c r="W145" t="s">
-        <v>607</v>
+        <v>145</v>
       </c>
     </row>
     <row r="146" spans="1:23">
@@ -15344,28 +15341,28 @@
         <v>463</v>
       </c>
       <c r="C146">
-        <v>6931</v>
+        <v>3500.7</v>
       </c>
       <c r="D146">
-        <v>50.27</v>
+        <v>56.68</v>
       </c>
       <c r="E146">
-        <v>7061.74</v>
+        <v>3550.63</v>
       </c>
       <c r="F146">
-        <v>7136.81</v>
+        <v>3537.49</v>
       </c>
       <c r="G146">
-        <v>6986.95</v>
+        <v>3359.84</v>
       </c>
       <c r="H146">
-        <v>6338.76</v>
+        <v>3288.45</v>
       </c>
       <c r="I146">
-        <v>254364</v>
+        <v>162504</v>
       </c>
       <c r="J146">
-        <v>400417</v>
+        <v>254310</v>
       </c>
       <c r="K146">
         <v>0.64</v>
@@ -15377,22 +15374,22 @@
         <v>118</v>
       </c>
       <c r="N146">
-        <v>7279.05</v>
+        <v>3595</v>
       </c>
       <c r="O146">
-        <v>203.24</v>
+        <v>94.75</v>
       </c>
       <c r="P146">
-        <v>6626.14</v>
+        <v>3358.57</v>
       </c>
       <c r="Q146">
-        <v>7540.71</v>
+        <v>3784.95</v>
       </c>
       <c r="R146">
-        <v>4.4</v>
+        <v>4.06</v>
       </c>
       <c r="S146">
-        <v>8.800000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="T146" t="s">
         <v>155</v>
@@ -15404,7 +15401,7 @@
         <v>591</v>
       </c>
       <c r="W146" t="s">
-        <v>145</v>
+        <v>607</v>
       </c>
     </row>
     <row r="147" spans="1:23">
@@ -15770,28 +15767,28 @@
         <v>469</v>
       </c>
       <c r="C152">
-        <v>155.99</v>
+        <v>1412</v>
       </c>
       <c r="D152">
-        <v>51.38</v>
+        <v>55.01</v>
       </c>
       <c r="E152">
-        <v>159.96</v>
+        <v>1451.05</v>
       </c>
       <c r="F152">
-        <v>157.33</v>
+        <v>1355</v>
       </c>
       <c r="G152">
-        <v>152.92</v>
+        <v>1270.63</v>
       </c>
       <c r="H152">
-        <v>152.38</v>
+        <v>1365.5</v>
       </c>
       <c r="I152">
-        <v>371890</v>
+        <v>1845056</v>
       </c>
       <c r="J152">
-        <v>721231</v>
+        <v>3517963</v>
       </c>
       <c r="K152">
         <v>0.52</v>
@@ -15803,22 +15800,22 @@
         <v>118</v>
       </c>
       <c r="N152">
-        <v>137.72</v>
+        <v>1541.19</v>
       </c>
       <c r="O152">
-        <v>6.08</v>
+        <v>54.55</v>
       </c>
       <c r="P152">
-        <v>146.86</v>
+        <v>1330.18</v>
       </c>
       <c r="Q152">
-        <v>174.24</v>
+        <v>1575.65</v>
       </c>
       <c r="R152">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="S152">
-        <v>11.7</v>
+        <v>11.59</v>
       </c>
       <c r="T152" t="s">
         <v>155</v>
@@ -15830,7 +15827,7 @@
         <v>591</v>
       </c>
       <c r="W152" t="s">
-        <v>128</v>
+        <v>601</v>
       </c>
     </row>
     <row r="153" spans="1:23">
@@ -15841,28 +15838,28 @@
         <v>470</v>
       </c>
       <c r="C153">
-        <v>1412</v>
+        <v>155.99</v>
       </c>
       <c r="D153">
-        <v>55.01</v>
+        <v>51.38</v>
       </c>
       <c r="E153">
-        <v>1451.05</v>
+        <v>159.96</v>
       </c>
       <c r="F153">
-        <v>1355</v>
+        <v>157.33</v>
       </c>
       <c r="G153">
-        <v>1270.63</v>
+        <v>152.92</v>
       </c>
       <c r="H153">
-        <v>1365.5</v>
+        <v>152.38</v>
       </c>
       <c r="I153">
-        <v>1845056</v>
+        <v>371890</v>
       </c>
       <c r="J153">
-        <v>3517963</v>
+        <v>721231</v>
       </c>
       <c r="K153">
         <v>0.52</v>
@@ -15874,22 +15871,22 @@
         <v>118</v>
       </c>
       <c r="N153">
-        <v>1541.19</v>
+        <v>137.72</v>
       </c>
       <c r="O153">
-        <v>54.55</v>
+        <v>6.08</v>
       </c>
       <c r="P153">
-        <v>1330.18</v>
+        <v>146.86</v>
       </c>
       <c r="Q153">
-        <v>1575.65</v>
+        <v>174.24</v>
       </c>
       <c r="R153">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="S153">
-        <v>11.59</v>
+        <v>11.7</v>
       </c>
       <c r="T153" t="s">
         <v>155</v>
@@ -15901,7 +15898,7 @@
         <v>591</v>
       </c>
       <c r="W153" t="s">
-        <v>601</v>
+        <v>128</v>
       </c>
     </row>
     <row r="154" spans="1:23">
@@ -17119,28 +17116,28 @@
         <v>488</v>
       </c>
       <c r="C171">
-        <v>1475.8</v>
+        <v>234.21</v>
       </c>
       <c r="D171">
-        <v>41.7</v>
+        <v>45.42</v>
       </c>
       <c r="E171">
-        <v>1491.72</v>
+        <v>234.73</v>
       </c>
       <c r="F171">
-        <v>1491.94</v>
+        <v>233.08</v>
       </c>
       <c r="G171">
-        <v>1501.78</v>
+        <v>231.79</v>
       </c>
       <c r="H171">
-        <v>1600.42</v>
+        <v>243.11</v>
       </c>
       <c r="I171">
-        <v>52933</v>
+        <v>9959663</v>
       </c>
       <c r="J171">
-        <v>58352</v>
+        <v>10973784</v>
       </c>
       <c r="K171">
         <v>0.91</v>
@@ -17152,22 +17149,22 @@
         <v>118</v>
       </c>
       <c r="N171">
-        <v>1597.86</v>
+        <v>246</v>
       </c>
       <c r="O171">
-        <v>36.06</v>
+        <v>5.65</v>
       </c>
       <c r="P171">
-        <v>1421.7</v>
+        <v>225.74</v>
       </c>
       <c r="Q171">
-        <v>1583.99</v>
+        <v>251.15</v>
       </c>
       <c r="R171">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="S171">
-        <v>7.33</v>
+        <v>7.23</v>
       </c>
       <c r="T171" t="s">
         <v>155</v>
@@ -17179,7 +17176,7 @@
         <v>593</v>
       </c>
       <c r="W171" t="s">
-        <v>604</v>
+        <v>128</v>
       </c>
     </row>
     <row r="172" spans="1:23">
@@ -17190,28 +17187,28 @@
         <v>489</v>
       </c>
       <c r="C172">
-        <v>234.21</v>
+        <v>1475.8</v>
       </c>
       <c r="D172">
-        <v>45.42</v>
+        <v>41.7</v>
       </c>
       <c r="E172">
-        <v>234.73</v>
+        <v>1491.72</v>
       </c>
       <c r="F172">
-        <v>233.08</v>
+        <v>1491.94</v>
       </c>
       <c r="G172">
-        <v>231.79</v>
+        <v>1501.78</v>
       </c>
       <c r="H172">
-        <v>243.11</v>
+        <v>1600.42</v>
       </c>
       <c r="I172">
-        <v>9959663</v>
+        <v>52933</v>
       </c>
       <c r="J172">
-        <v>10973784</v>
+        <v>58352</v>
       </c>
       <c r="K172">
         <v>0.91</v>
@@ -17223,22 +17220,22 @@
         <v>118</v>
       </c>
       <c r="N172">
-        <v>246</v>
+        <v>1597.86</v>
       </c>
       <c r="O172">
-        <v>5.65</v>
+        <v>36.06</v>
       </c>
       <c r="P172">
-        <v>225.74</v>
+        <v>1421.7</v>
       </c>
       <c r="Q172">
-        <v>251.15</v>
+        <v>1583.99</v>
       </c>
       <c r="R172">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="S172">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="T172" t="s">
         <v>155</v>
@@ -17250,7 +17247,7 @@
         <v>593</v>
       </c>
       <c r="W172" t="s">
-        <v>128</v>
+        <v>604</v>
       </c>
     </row>
     <row r="173" spans="1:23">
@@ -17261,28 +17258,28 @@
         <v>490</v>
       </c>
       <c r="C173">
-        <v>1632.5</v>
+        <v>851.65</v>
       </c>
       <c r="D173">
-        <v>47.11</v>
+        <v>34.53</v>
       </c>
       <c r="E173">
-        <v>1648.34</v>
+        <v>858.78</v>
       </c>
       <c r="F173">
-        <v>1663.75</v>
+        <v>873.15</v>
       </c>
       <c r="G173">
-        <v>1623.45</v>
+        <v>916.36</v>
       </c>
       <c r="H173">
-        <v>1585.35</v>
+        <v>983.59</v>
       </c>
       <c r="I173">
-        <v>331753</v>
+        <v>146674</v>
       </c>
       <c r="J173">
-        <v>371209</v>
+        <v>165515</v>
       </c>
       <c r="K173">
         <v>0.89</v>
@@ -17294,22 +17291,22 @@
         <v>118</v>
       </c>
       <c r="N173">
-        <v>1741.41</v>
+        <v>907.28</v>
       </c>
       <c r="O173">
-        <v>45.19</v>
+        <v>26.51</v>
       </c>
       <c r="P173">
-        <v>1564.72</v>
+        <v>811.89</v>
       </c>
       <c r="Q173">
-        <v>1768.07</v>
+        <v>931.1799999999999</v>
       </c>
       <c r="R173">
-        <v>4.15</v>
+        <v>4.67</v>
       </c>
       <c r="S173">
-        <v>8.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="T173" t="s">
         <v>155</v>
@@ -17321,7 +17318,7 @@
         <v>593</v>
       </c>
       <c r="W173" t="s">
-        <v>611</v>
+        <v>144</v>
       </c>
     </row>
     <row r="174" spans="1:23">
@@ -17332,28 +17329,28 @@
         <v>491</v>
       </c>
       <c r="C174">
-        <v>851.65</v>
+        <v>1632.5</v>
       </c>
       <c r="D174">
-        <v>34.53</v>
+        <v>47.11</v>
       </c>
       <c r="E174">
-        <v>858.78</v>
+        <v>1648.34</v>
       </c>
       <c r="F174">
-        <v>873.15</v>
+        <v>1663.75</v>
       </c>
       <c r="G174">
-        <v>916.36</v>
+        <v>1623.45</v>
       </c>
       <c r="H174">
-        <v>983.59</v>
+        <v>1585.35</v>
       </c>
       <c r="I174">
-        <v>146674</v>
+        <v>331753</v>
       </c>
       <c r="J174">
-        <v>165515</v>
+        <v>371209</v>
       </c>
       <c r="K174">
         <v>0.89</v>
@@ -17365,22 +17362,22 @@
         <v>118</v>
       </c>
       <c r="N174">
-        <v>907.28</v>
+        <v>1741.41</v>
       </c>
       <c r="O174">
-        <v>26.51</v>
+        <v>45.19</v>
       </c>
       <c r="P174">
-        <v>811.89</v>
+        <v>1564.72</v>
       </c>
       <c r="Q174">
-        <v>931.1799999999999</v>
+        <v>1768.07</v>
       </c>
       <c r="R174">
-        <v>4.67</v>
+        <v>4.15</v>
       </c>
       <c r="S174">
-        <v>9.34</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T174" t="s">
         <v>155</v>
@@ -17392,7 +17389,7 @@
         <v>593</v>
       </c>
       <c r="W174" t="s">
-        <v>144</v>
+        <v>611</v>
       </c>
     </row>
     <row r="175" spans="1:23">
@@ -17900,28 +17897,28 @@
         <v>499</v>
       </c>
       <c r="C182">
-        <v>2194.7</v>
+        <v>14309</v>
       </c>
       <c r="D182">
-        <v>32.37</v>
+        <v>44.29</v>
       </c>
       <c r="E182">
-        <v>2186.48</v>
+        <v>14475.72</v>
       </c>
       <c r="F182">
-        <v>2255.96</v>
+        <v>14571.14</v>
       </c>
       <c r="G182">
-        <v>2284.89</v>
+        <v>14682.44</v>
       </c>
       <c r="H182">
-        <v>2363.69</v>
+        <v>14520.86</v>
       </c>
       <c r="I182">
-        <v>84767</v>
+        <v>9977</v>
       </c>
       <c r="J182">
-        <v>101893</v>
+        <v>11958</v>
       </c>
       <c r="K182">
         <v>0.83</v>
@@ -17933,22 +17930,22 @@
         <v>118</v>
       </c>
       <c r="N182">
-        <v>2456.73</v>
+        <v>15149.61</v>
       </c>
       <c r="O182">
-        <v>48.72</v>
+        <v>410.23</v>
       </c>
       <c r="P182">
-        <v>2121.61</v>
+        <v>13693.65</v>
       </c>
       <c r="Q182">
-        <v>2340.87</v>
+        <v>15539.7</v>
       </c>
       <c r="R182">
-        <v>3.33</v>
+        <v>4.3</v>
       </c>
       <c r="S182">
-        <v>6.66</v>
+        <v>8.6</v>
       </c>
       <c r="T182" t="s">
         <v>155</v>
@@ -17960,7 +17957,7 @@
         <v>593</v>
       </c>
       <c r="W182" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="183" spans="1:23">
@@ -17971,28 +17968,28 @@
         <v>500</v>
       </c>
       <c r="C183">
-        <v>649.5</v>
+        <v>2194.7</v>
       </c>
       <c r="D183">
-        <v>35.76</v>
+        <v>32.37</v>
       </c>
       <c r="E183">
-        <v>642.6900000000001</v>
+        <v>2186.48</v>
       </c>
       <c r="F183">
-        <v>665.45</v>
+        <v>2255.96</v>
       </c>
       <c r="G183">
-        <v>661.25</v>
+        <v>2284.89</v>
       </c>
       <c r="H183">
-        <v>674.02</v>
+        <v>2363.69</v>
       </c>
       <c r="I183">
-        <v>206205</v>
+        <v>84767</v>
       </c>
       <c r="J183">
-        <v>247934</v>
+        <v>101893</v>
       </c>
       <c r="K183">
         <v>0.83</v>
@@ -18004,22 +18001,22 @@
         <v>118</v>
       </c>
       <c r="N183">
-        <v>797.53</v>
+        <v>2456.73</v>
       </c>
       <c r="O183">
-        <v>19.41</v>
+        <v>48.72</v>
       </c>
       <c r="P183">
-        <v>620.39</v>
+        <v>2121.61</v>
       </c>
       <c r="Q183">
-        <v>707.72</v>
+        <v>2340.87</v>
       </c>
       <c r="R183">
-        <v>4.48</v>
+        <v>3.33</v>
       </c>
       <c r="S183">
-        <v>8.960000000000001</v>
+        <v>6.66</v>
       </c>
       <c r="T183" t="s">
         <v>155</v>
@@ -18031,7 +18028,7 @@
         <v>593</v>
       </c>
       <c r="W183" t="s">
-        <v>611</v>
+        <v>129</v>
       </c>
     </row>
     <row r="184" spans="1:23">
@@ -18042,28 +18039,28 @@
         <v>501</v>
       </c>
       <c r="C184">
-        <v>2090.8</v>
+        <v>649.5</v>
       </c>
       <c r="D184">
-        <v>29.54</v>
+        <v>35.76</v>
       </c>
       <c r="E184">
-        <v>2119.9</v>
+        <v>642.6900000000001</v>
       </c>
       <c r="F184">
-        <v>2179.16</v>
+        <v>665.45</v>
       </c>
       <c r="G184">
-        <v>2211.7</v>
+        <v>661.25</v>
       </c>
       <c r="H184">
-        <v>2292.76</v>
+        <v>674.02</v>
       </c>
       <c r="I184">
-        <v>22096</v>
+        <v>206205</v>
       </c>
       <c r="J184">
-        <v>26606</v>
+        <v>247934</v>
       </c>
       <c r="K184">
         <v>0.83</v>
@@ -18075,22 +18072,22 @@
         <v>118</v>
       </c>
       <c r="N184">
-        <v>2250.38</v>
+        <v>797.53</v>
       </c>
       <c r="O184">
-        <v>56.41</v>
+        <v>19.41</v>
       </c>
       <c r="P184">
-        <v>2006.19</v>
+        <v>620.39</v>
       </c>
       <c r="Q184">
-        <v>2260.02</v>
+        <v>707.72</v>
       </c>
       <c r="R184">
-        <v>4.05</v>
+        <v>4.48</v>
       </c>
       <c r="S184">
-        <v>8.09</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="T184" t="s">
         <v>155</v>
@@ -18102,7 +18099,7 @@
         <v>593</v>
       </c>
       <c r="W184" t="s">
-        <v>138</v>
+        <v>611</v>
       </c>
     </row>
     <row r="185" spans="1:23">
@@ -18113,28 +18110,28 @@
         <v>502</v>
       </c>
       <c r="C185">
-        <v>14309</v>
+        <v>2090.8</v>
       </c>
       <c r="D185">
-        <v>44.29</v>
+        <v>29.54</v>
       </c>
       <c r="E185">
-        <v>14475.72</v>
+        <v>2119.9</v>
       </c>
       <c r="F185">
-        <v>14571.14</v>
+        <v>2179.16</v>
       </c>
       <c r="G185">
-        <v>14682.44</v>
+        <v>2211.7</v>
       </c>
       <c r="H185">
-        <v>14520.86</v>
+        <v>2292.76</v>
       </c>
       <c r="I185">
-        <v>9977</v>
+        <v>22096</v>
       </c>
       <c r="J185">
-        <v>11958</v>
+        <v>26606</v>
       </c>
       <c r="K185">
         <v>0.83</v>
@@ -18146,22 +18143,22 @@
         <v>118</v>
       </c>
       <c r="N185">
-        <v>15149.61</v>
+        <v>2250.38</v>
       </c>
       <c r="O185">
-        <v>410.23</v>
+        <v>56.41</v>
       </c>
       <c r="P185">
-        <v>13693.65</v>
+        <v>2006.19</v>
       </c>
       <c r="Q185">
-        <v>15539.7</v>
+        <v>2260.02</v>
       </c>
       <c r="R185">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="S185">
-        <v>8.6</v>
+        <v>8.09</v>
       </c>
       <c r="T185" t="s">
         <v>155</v>
@@ -18173,7 +18170,7 @@
         <v>593</v>
       </c>
       <c r="W185" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="186" spans="1:23">
@@ -18394,28 +18391,28 @@
         <v>506</v>
       </c>
       <c r="C189">
-        <v>3137.3</v>
+        <v>1257.2</v>
       </c>
       <c r="D189">
-        <v>40.27</v>
+        <v>44.2</v>
       </c>
       <c r="E189">
-        <v>3153.21</v>
+        <v>1255.49</v>
       </c>
       <c r="F189">
-        <v>3188.74</v>
+        <v>1265.62</v>
       </c>
       <c r="G189">
-        <v>3324.07</v>
+        <v>1279.21</v>
       </c>
       <c r="H189">
-        <v>3563.37</v>
+        <v>1304.48</v>
       </c>
       <c r="I189">
-        <v>55980</v>
+        <v>555079</v>
       </c>
       <c r="J189">
-        <v>73023</v>
+        <v>719227</v>
       </c>
       <c r="K189">
         <v>0.77</v>
@@ -18427,22 +18424,22 @@
         <v>118</v>
       </c>
       <c r="N189">
-        <v>3846.43</v>
+        <v>1405.23</v>
       </c>
       <c r="O189">
-        <v>89.40000000000001</v>
+        <v>27.45</v>
       </c>
       <c r="P189">
-        <v>3003.21</v>
+        <v>1216.03</v>
       </c>
       <c r="Q189">
-        <v>3405.49</v>
+        <v>1339.54</v>
       </c>
       <c r="R189">
-        <v>4.27</v>
+        <v>3.27</v>
       </c>
       <c r="S189">
-        <v>8.550000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="T189" t="s">
         <v>155</v>
@@ -18454,7 +18451,7 @@
         <v>593</v>
       </c>
       <c r="W189" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="190" spans="1:23">
@@ -18465,28 +18462,28 @@
         <v>507</v>
       </c>
       <c r="C190">
-        <v>1257.2</v>
+        <v>3137.3</v>
       </c>
       <c r="D190">
-        <v>44.2</v>
+        <v>40.27</v>
       </c>
       <c r="E190">
-        <v>1255.49</v>
+        <v>3153.21</v>
       </c>
       <c r="F190">
-        <v>1265.62</v>
+        <v>3188.74</v>
       </c>
       <c r="G190">
-        <v>1279.21</v>
+        <v>3324.07</v>
       </c>
       <c r="H190">
-        <v>1304.48</v>
+        <v>3563.37</v>
       </c>
       <c r="I190">
-        <v>555079</v>
+        <v>55980</v>
       </c>
       <c r="J190">
-        <v>719227</v>
+        <v>73023</v>
       </c>
       <c r="K190">
         <v>0.77</v>
@@ -18498,22 +18495,22 @@
         <v>118</v>
       </c>
       <c r="N190">
-        <v>1405.23</v>
+        <v>3846.43</v>
       </c>
       <c r="O190">
-        <v>27.45</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="P190">
-        <v>1216.03</v>
+        <v>3003.21</v>
       </c>
       <c r="Q190">
-        <v>1339.54</v>
+        <v>3405.49</v>
       </c>
       <c r="R190">
-        <v>3.27</v>
+        <v>4.27</v>
       </c>
       <c r="S190">
-        <v>6.55</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="T190" t="s">
         <v>155</v>
@@ -18525,7 +18522,7 @@
         <v>593</v>
       </c>
       <c r="W190" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="191" spans="1:23">
@@ -18962,28 +18959,28 @@
         <v>514</v>
       </c>
       <c r="C197">
-        <v>265.55</v>
+        <v>6828.5</v>
       </c>
       <c r="D197">
-        <v>40.23</v>
+        <v>43.79</v>
       </c>
       <c r="E197">
-        <v>269.18</v>
+        <v>7101.08</v>
       </c>
       <c r="F197">
-        <v>274.99</v>
+        <v>7130.88</v>
       </c>
       <c r="G197">
-        <v>283.1</v>
+        <v>7040.18</v>
       </c>
       <c r="H197">
-        <v>296.19</v>
+        <v>6876.83</v>
       </c>
       <c r="I197">
-        <v>3578915</v>
+        <v>82138</v>
       </c>
       <c r="J197">
-        <v>4975308</v>
+        <v>114388</v>
       </c>
       <c r="K197">
         <v>0.72</v>
@@ -18995,22 +18992,22 @@
         <v>118</v>
       </c>
       <c r="N197">
-        <v>302.55</v>
+        <v>6316.11</v>
       </c>
       <c r="O197">
-        <v>8.16</v>
+        <v>202.22</v>
       </c>
       <c r="P197">
-        <v>253.31</v>
+        <v>6525.17</v>
       </c>
       <c r="Q197">
-        <v>290.03</v>
+        <v>7435.15</v>
       </c>
       <c r="R197">
-        <v>4.61</v>
+        <v>4.44</v>
       </c>
       <c r="S197">
-        <v>9.220000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="T197" t="s">
         <v>155</v>
@@ -19022,7 +19019,7 @@
         <v>593</v>
       </c>
       <c r="W197" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="198" spans="1:23">
@@ -19033,28 +19030,28 @@
         <v>515</v>
       </c>
       <c r="C198">
-        <v>6828.5</v>
+        <v>265.55</v>
       </c>
       <c r="D198">
-        <v>43.79</v>
+        <v>40.23</v>
       </c>
       <c r="E198">
-        <v>7101.08</v>
+        <v>269.18</v>
       </c>
       <c r="F198">
-        <v>7130.88</v>
+        <v>274.99</v>
       </c>
       <c r="G198">
-        <v>7040.18</v>
+        <v>283.1</v>
       </c>
       <c r="H198">
-        <v>6876.83</v>
+        <v>296.19</v>
       </c>
       <c r="I198">
-        <v>82138</v>
+        <v>3578915</v>
       </c>
       <c r="J198">
-        <v>114388</v>
+        <v>4975308</v>
       </c>
       <c r="K198">
         <v>0.72</v>
@@ -19066,22 +19063,22 @@
         <v>118</v>
       </c>
       <c r="N198">
-        <v>6316.11</v>
+        <v>302.55</v>
       </c>
       <c r="O198">
-        <v>202.22</v>
+        <v>8.16</v>
       </c>
       <c r="P198">
-        <v>6525.17</v>
+        <v>253.31</v>
       </c>
       <c r="Q198">
-        <v>7435.15</v>
+        <v>290.03</v>
       </c>
       <c r="R198">
-        <v>4.44</v>
+        <v>4.61</v>
       </c>
       <c r="S198">
-        <v>8.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="T198" t="s">
         <v>155</v>
@@ -19093,7 +19090,7 @@
         <v>593</v>
       </c>
       <c r="W198" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="199" spans="1:23">
@@ -19672,28 +19669,28 @@
         <v>524</v>
       </c>
       <c r="C207">
-        <v>628.4</v>
+        <v>1013.2</v>
       </c>
       <c r="D207">
-        <v>42.94</v>
+        <v>45.22</v>
       </c>
       <c r="E207">
-        <v>638.08</v>
+        <v>999.77</v>
       </c>
       <c r="F207">
-        <v>630.84</v>
+        <v>1006.02</v>
       </c>
       <c r="G207">
-        <v>634.91</v>
+        <v>1027.52</v>
       </c>
       <c r="H207">
-        <v>672.1799999999999</v>
+        <v>1060.56</v>
       </c>
       <c r="I207">
-        <v>1324061</v>
+        <v>975781</v>
       </c>
       <c r="J207">
-        <v>2004034</v>
+        <v>1481842</v>
       </c>
       <c r="K207">
         <v>0.66</v>
@@ -19705,22 +19702,22 @@
         <v>118</v>
       </c>
       <c r="N207">
-        <v>644.09</v>
+        <v>1025.44</v>
       </c>
       <c r="O207">
-        <v>14</v>
+        <v>25.49</v>
       </c>
       <c r="P207">
-        <v>607.4</v>
+        <v>974.96</v>
       </c>
       <c r="Q207">
-        <v>670.4</v>
+        <v>1089.67</v>
       </c>
       <c r="R207">
-        <v>3.34</v>
+        <v>3.77</v>
       </c>
       <c r="S207">
-        <v>6.68</v>
+        <v>7.55</v>
       </c>
       <c r="T207" t="s">
         <v>155</v>
@@ -19743,28 +19740,28 @@
         <v>525</v>
       </c>
       <c r="C208">
-        <v>1013.2</v>
+        <v>628.4</v>
       </c>
       <c r="D208">
-        <v>45.22</v>
+        <v>42.94</v>
       </c>
       <c r="E208">
-        <v>999.77</v>
+        <v>638.08</v>
       </c>
       <c r="F208">
-        <v>1006.02</v>
+        <v>630.84</v>
       </c>
       <c r="G208">
-        <v>1027.52</v>
+        <v>634.91</v>
       </c>
       <c r="H208">
-        <v>1060.56</v>
+        <v>672.1799999999999</v>
       </c>
       <c r="I208">
-        <v>975781</v>
+        <v>1324061</v>
       </c>
       <c r="J208">
-        <v>1481842</v>
+        <v>2004034</v>
       </c>
       <c r="K208">
         <v>0.66</v>
@@ -19776,22 +19773,22 @@
         <v>118</v>
       </c>
       <c r="N208">
-        <v>1025.44</v>
+        <v>644.09</v>
       </c>
       <c r="O208">
-        <v>25.49</v>
+        <v>14</v>
       </c>
       <c r="P208">
-        <v>974.96</v>
+        <v>607.4</v>
       </c>
       <c r="Q208">
-        <v>1089.67</v>
+        <v>670.4</v>
       </c>
       <c r="R208">
-        <v>3.77</v>
+        <v>3.34</v>
       </c>
       <c r="S208">
-        <v>7.55</v>
+        <v>6.68</v>
       </c>
       <c r="T208" t="s">
         <v>155</v>
@@ -20311,28 +20308,28 @@
         <v>533</v>
       </c>
       <c r="C216">
-        <v>1150.5</v>
+        <v>289.1</v>
       </c>
       <c r="D216">
-        <v>38.24</v>
+        <v>43.21</v>
       </c>
       <c r="E216">
-        <v>1151.9</v>
+        <v>292.44</v>
       </c>
       <c r="F216">
-        <v>1166.48</v>
+        <v>288.38</v>
       </c>
       <c r="G216">
-        <v>1187.97</v>
+        <v>298</v>
       </c>
       <c r="H216">
-        <v>1226.18</v>
+        <v>320.54</v>
       </c>
       <c r="I216">
-        <v>692180</v>
+        <v>5025923</v>
       </c>
       <c r="J216">
-        <v>1149289</v>
+        <v>8339410</v>
       </c>
       <c r="K216">
         <v>0.6</v>
@@ -20344,22 +20341,22 @@
         <v>118</v>
       </c>
       <c r="N216">
-        <v>1150.53</v>
+        <v>302.91</v>
       </c>
       <c r="O216">
-        <v>28.9</v>
+        <v>8.08</v>
       </c>
       <c r="P216">
-        <v>1107.14</v>
+        <v>276.98</v>
       </c>
       <c r="Q216">
-        <v>1237.21</v>
+        <v>313.34</v>
       </c>
       <c r="R216">
-        <v>3.77</v>
+        <v>4.19</v>
       </c>
       <c r="S216">
-        <v>7.54</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="T216" t="s">
         <v>155</v>
@@ -20371,7 +20368,7 @@
         <v>593</v>
       </c>
       <c r="W216" t="s">
-        <v>145</v>
+        <v>605</v>
       </c>
     </row>
     <row r="217" spans="1:23">
@@ -20382,28 +20379,28 @@
         <v>534</v>
       </c>
       <c r="C217">
-        <v>1017</v>
+        <v>171.68</v>
       </c>
       <c r="D217">
-        <v>36.03</v>
+        <v>39.98</v>
       </c>
       <c r="E217">
-        <v>1076.92</v>
+        <v>178.96</v>
       </c>
       <c r="F217">
-        <v>1122.48</v>
+        <v>182.72</v>
       </c>
       <c r="G217">
-        <v>1087.34</v>
+        <v>176.75</v>
       </c>
       <c r="H217">
-        <v>1013.52</v>
+        <v>171.09</v>
       </c>
       <c r="I217">
-        <v>146493</v>
+        <v>1150340</v>
       </c>
       <c r="J217">
-        <v>245046</v>
+        <v>1912617</v>
       </c>
       <c r="K217">
         <v>0.6</v>
@@ -20415,22 +20412,22 @@
         <v>118</v>
       </c>
       <c r="N217">
-        <v>1184.2</v>
+        <v>180.34</v>
       </c>
       <c r="O217">
-        <v>45.89</v>
+        <v>5.54</v>
       </c>
       <c r="P217">
-        <v>948.17</v>
+        <v>163.37</v>
       </c>
       <c r="Q217">
-        <v>1154.67</v>
+        <v>188.3</v>
       </c>
       <c r="R217">
-        <v>6.77</v>
+        <v>4.84</v>
       </c>
       <c r="S217">
-        <v>13.54</v>
+        <v>9.68</v>
       </c>
       <c r="T217" t="s">
         <v>155</v>
@@ -20442,7 +20439,7 @@
         <v>593</v>
       </c>
       <c r="W217" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218" spans="1:23">
@@ -20453,28 +20450,28 @@
         <v>535</v>
       </c>
       <c r="C218">
-        <v>289.1</v>
+        <v>1150.5</v>
       </c>
       <c r="D218">
-        <v>43.21</v>
+        <v>38.24</v>
       </c>
       <c r="E218">
-        <v>292.44</v>
+        <v>1151.9</v>
       </c>
       <c r="F218">
-        <v>288.38</v>
+        <v>1166.48</v>
       </c>
       <c r="G218">
-        <v>298</v>
+        <v>1187.97</v>
       </c>
       <c r="H218">
-        <v>320.54</v>
+        <v>1226.18</v>
       </c>
       <c r="I218">
-        <v>5025923</v>
+        <v>692180</v>
       </c>
       <c r="J218">
-        <v>8339410</v>
+        <v>1149289</v>
       </c>
       <c r="K218">
         <v>0.6</v>
@@ -20486,22 +20483,22 @@
         <v>118</v>
       </c>
       <c r="N218">
-        <v>302.91</v>
+        <v>1150.53</v>
       </c>
       <c r="O218">
-        <v>8.08</v>
+        <v>28.9</v>
       </c>
       <c r="P218">
-        <v>276.98</v>
+        <v>1107.14</v>
       </c>
       <c r="Q218">
-        <v>313.34</v>
+        <v>1237.21</v>
       </c>
       <c r="R218">
-        <v>4.19</v>
+        <v>3.77</v>
       </c>
       <c r="S218">
-        <v>8.380000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="T218" t="s">
         <v>155</v>
@@ -20513,7 +20510,7 @@
         <v>593</v>
       </c>
       <c r="W218" t="s">
-        <v>605</v>
+        <v>145</v>
       </c>
     </row>
     <row r="219" spans="1:23">
@@ -20524,28 +20521,28 @@
         <v>536</v>
       </c>
       <c r="C219">
-        <v>171.68</v>
+        <v>1017</v>
       </c>
       <c r="D219">
-        <v>39.98</v>
+        <v>36.03</v>
       </c>
       <c r="E219">
-        <v>178.96</v>
+        <v>1076.92</v>
       </c>
       <c r="F219">
-        <v>182.72</v>
+        <v>1122.48</v>
       </c>
       <c r="G219">
-        <v>176.75</v>
+        <v>1087.34</v>
       </c>
       <c r="H219">
-        <v>171.09</v>
+        <v>1013.52</v>
       </c>
       <c r="I219">
-        <v>1150340</v>
+        <v>146493</v>
       </c>
       <c r="J219">
-        <v>1912617</v>
+        <v>245046</v>
       </c>
       <c r="K219">
         <v>0.6</v>
@@ -20557,22 +20554,22 @@
         <v>118</v>
       </c>
       <c r="N219">
-        <v>180.34</v>
+        <v>1184.2</v>
       </c>
       <c r="O219">
-        <v>5.54</v>
+        <v>45.89</v>
       </c>
       <c r="P219">
-        <v>163.37</v>
+        <v>948.17</v>
       </c>
       <c r="Q219">
-        <v>188.3</v>
+        <v>1154.67</v>
       </c>
       <c r="R219">
-        <v>4.84</v>
+        <v>6.77</v>
       </c>
       <c r="S219">
-        <v>9.68</v>
+        <v>13.54</v>
       </c>
       <c r="T219" t="s">
         <v>155</v>
@@ -20584,7 +20581,7 @@
         <v>593</v>
       </c>
       <c r="W219" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
     </row>
     <row r="220" spans="1:23">
@@ -22370,28 +22367,28 @@
         <v>562</v>
       </c>
       <c r="C245">
-        <v>2177</v>
+        <v>4081</v>
       </c>
       <c r="D245">
-        <v>69.95</v>
+        <v>49.95</v>
       </c>
       <c r="E245">
-        <v>2185.79</v>
+        <v>4061.54</v>
       </c>
       <c r="F245">
-        <v>2058.93</v>
+        <v>4112.09</v>
       </c>
       <c r="G245">
-        <v>1876.46</v>
+        <v>4095.68</v>
       </c>
       <c r="H245">
-        <v>1681.1</v>
+        <v>4056.98</v>
       </c>
       <c r="I245">
-        <v>368490</v>
+        <v>41013</v>
       </c>
       <c r="J245">
-        <v>810004</v>
+        <v>91273</v>
       </c>
       <c r="K245">
         <v>0.45</v>
@@ -22403,22 +22400,22 @@
         <v>118</v>
       </c>
       <c r="N245">
-        <v>1448.22</v>
+        <v>4155.67</v>
       </c>
       <c r="O245">
-        <v>86.76000000000001</v>
+        <v>108.24</v>
       </c>
       <c r="P245">
-        <v>2046.87</v>
+        <v>3918.65</v>
       </c>
       <c r="Q245">
-        <v>2437.27</v>
+        <v>4405.71</v>
       </c>
       <c r="R245">
-        <v>5.98</v>
+        <v>3.98</v>
       </c>
       <c r="S245">
-        <v>11.96</v>
+        <v>7.96</v>
       </c>
       <c r="T245" t="s">
         <v>155</v>
@@ -22430,7 +22427,7 @@
         <v>593</v>
       </c>
       <c r="W245" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="246" spans="1:23">
@@ -22441,28 +22438,28 @@
         <v>563</v>
       </c>
       <c r="C246">
-        <v>4081</v>
+        <v>2177</v>
       </c>
       <c r="D246">
-        <v>49.95</v>
+        <v>69.95</v>
       </c>
       <c r="E246">
-        <v>4061.54</v>
+        <v>2185.79</v>
       </c>
       <c r="F246">
-        <v>4112.09</v>
+        <v>2058.93</v>
       </c>
       <c r="G246">
-        <v>4095.68</v>
+        <v>1876.46</v>
       </c>
       <c r="H246">
-        <v>4056.98</v>
+        <v>1681.1</v>
       </c>
       <c r="I246">
-        <v>41013</v>
+        <v>368490</v>
       </c>
       <c r="J246">
-        <v>91273</v>
+        <v>810004</v>
       </c>
       <c r="K246">
         <v>0.45</v>
@@ -22474,22 +22471,22 @@
         <v>118</v>
       </c>
       <c r="N246">
-        <v>4155.67</v>
+        <v>1448.22</v>
       </c>
       <c r="O246">
-        <v>108.24</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="P246">
-        <v>3918.65</v>
+        <v>2046.87</v>
       </c>
       <c r="Q246">
-        <v>4405.71</v>
+        <v>2437.27</v>
       </c>
       <c r="R246">
-        <v>3.98</v>
+        <v>5.98</v>
       </c>
       <c r="S246">
-        <v>7.96</v>
+        <v>11.96</v>
       </c>
       <c r="T246" t="s">
         <v>155</v>
@@ -22501,7 +22498,7 @@
         <v>593</v>
       </c>
       <c r="W246" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="247" spans="1:23">
@@ -22583,28 +22580,28 @@
         <v>565</v>
       </c>
       <c r="C248">
-        <v>416</v>
+        <v>740.2</v>
       </c>
       <c r="D248">
-        <v>37.28</v>
+        <v>33.77</v>
       </c>
       <c r="E248">
-        <v>426.73</v>
+        <v>759.35</v>
       </c>
       <c r="F248">
-        <v>424</v>
+        <v>781.61</v>
       </c>
       <c r="G248">
-        <v>425.69</v>
+        <v>769.21</v>
       </c>
       <c r="H248">
-        <v>450.91</v>
+        <v>790.4400000000001</v>
       </c>
       <c r="I248">
-        <v>1816420</v>
+        <v>24353</v>
       </c>
       <c r="J248">
-        <v>4189743</v>
+        <v>56473</v>
       </c>
       <c r="K248">
         <v>0.43</v>
@@ -22616,22 +22613,22 @@
         <v>118</v>
       </c>
       <c r="N248">
-        <v>451.23</v>
+        <v>776.12</v>
       </c>
       <c r="O248">
-        <v>11.78</v>
+        <v>25.15</v>
       </c>
       <c r="P248">
-        <v>398.33</v>
+        <v>702.47</v>
       </c>
       <c r="Q248">
-        <v>451.33</v>
+        <v>815.66</v>
       </c>
       <c r="R248">
-        <v>4.25</v>
+        <v>5.1</v>
       </c>
       <c r="S248">
-        <v>8.49</v>
+        <v>10.19</v>
       </c>
       <c r="T248" t="s">
         <v>155</v>
@@ -22643,7 +22640,7 @@
         <v>593</v>
       </c>
       <c r="W248" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="249" spans="1:23">
@@ -22654,28 +22651,28 @@
         <v>566</v>
       </c>
       <c r="C249">
-        <v>740.2</v>
+        <v>416</v>
       </c>
       <c r="D249">
-        <v>33.77</v>
+        <v>37.28</v>
       </c>
       <c r="E249">
-        <v>759.35</v>
+        <v>426.73</v>
       </c>
       <c r="F249">
-        <v>781.61</v>
+        <v>424</v>
       </c>
       <c r="G249">
-        <v>769.21</v>
+        <v>425.69</v>
       </c>
       <c r="H249">
-        <v>790.4400000000001</v>
+        <v>450.91</v>
       </c>
       <c r="I249">
-        <v>24353</v>
+        <v>1816420</v>
       </c>
       <c r="J249">
-        <v>56473</v>
+        <v>4189743</v>
       </c>
       <c r="K249">
         <v>0.43</v>
@@ -22687,22 +22684,22 @@
         <v>118</v>
       </c>
       <c r="N249">
-        <v>776.12</v>
+        <v>451.23</v>
       </c>
       <c r="O249">
-        <v>25.15</v>
+        <v>11.78</v>
       </c>
       <c r="P249">
-        <v>702.47</v>
+        <v>398.33</v>
       </c>
       <c r="Q249">
-        <v>815.66</v>
+        <v>451.33</v>
       </c>
       <c r="R249">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="S249">
-        <v>10.19</v>
+        <v>8.49</v>
       </c>
       <c r="T249" t="s">
         <v>155</v>
@@ -22714,7 +22711,7 @@
         <v>593</v>
       </c>
       <c r="W249" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="250" spans="1:23">
@@ -22867,28 +22864,28 @@
         <v>569</v>
       </c>
       <c r="C252">
-        <v>584.95</v>
+        <v>1458.1</v>
       </c>
       <c r="D252">
-        <v>28.37</v>
+        <v>35.92</v>
       </c>
       <c r="E252">
-        <v>590.13</v>
+        <v>1488.56</v>
       </c>
       <c r="F252">
-        <v>592.87</v>
+        <v>1543.78</v>
       </c>
       <c r="G252">
-        <v>611.65</v>
+        <v>1540.37</v>
       </c>
       <c r="H252">
-        <v>682.13</v>
+        <v>1629.3</v>
       </c>
       <c r="I252">
-        <v>506900</v>
+        <v>91972</v>
       </c>
       <c r="J252">
-        <v>1429504</v>
+        <v>260139</v>
       </c>
       <c r="K252">
         <v>0.35</v>
@@ -22900,22 +22897,22 @@
         <v>118</v>
       </c>
       <c r="N252">
-        <v>611.28</v>
+        <v>1557.08</v>
       </c>
       <c r="O252">
-        <v>13.75</v>
+        <v>53.25</v>
       </c>
       <c r="P252">
-        <v>564.33</v>
+        <v>1378.22</v>
       </c>
       <c r="Q252">
-        <v>626.2</v>
+        <v>1617.86</v>
       </c>
       <c r="R252">
-        <v>3.53</v>
+        <v>5.48</v>
       </c>
       <c r="S252">
-        <v>7.05</v>
+        <v>10.96</v>
       </c>
       <c r="T252" t="s">
         <v>155</v>
@@ -22938,28 +22935,28 @@
         <v>570</v>
       </c>
       <c r="C253">
-        <v>982.6</v>
+        <v>584.95</v>
       </c>
       <c r="D253">
-        <v>49.54</v>
+        <v>28.37</v>
       </c>
       <c r="E253">
-        <v>990.45</v>
+        <v>590.13</v>
       </c>
       <c r="F253">
-        <v>949.73</v>
+        <v>592.87</v>
       </c>
       <c r="G253">
-        <v>936.1</v>
+        <v>611.65</v>
       </c>
       <c r="H253">
-        <v>1006.05</v>
+        <v>682.13</v>
       </c>
       <c r="I253">
-        <v>915803</v>
+        <v>506900</v>
       </c>
       <c r="J253">
-        <v>2623676</v>
+        <v>1429504</v>
       </c>
       <c r="K253">
         <v>0.35</v>
@@ -22971,22 +22968,22 @@
         <v>118</v>
       </c>
       <c r="N253">
-        <v>1024.66</v>
+        <v>611.28</v>
       </c>
       <c r="O253">
-        <v>34.22</v>
+        <v>13.75</v>
       </c>
       <c r="P253">
-        <v>931.27</v>
+        <v>564.33</v>
       </c>
       <c r="Q253">
-        <v>1085.26</v>
+        <v>626.2</v>
       </c>
       <c r="R253">
-        <v>5.22</v>
+        <v>3.53</v>
       </c>
       <c r="S253">
-        <v>10.45</v>
+        <v>7.05</v>
       </c>
       <c r="T253" t="s">
         <v>155</v>
@@ -22998,7 +22995,7 @@
         <v>593</v>
       </c>
       <c r="W253" t="s">
-        <v>596</v>
+        <v>128</v>
       </c>
     </row>
     <row r="254" spans="1:23">
@@ -23009,28 +23006,28 @@
         <v>571</v>
       </c>
       <c r="C254">
-        <v>1458.1</v>
+        <v>982.6</v>
       </c>
       <c r="D254">
-        <v>35.92</v>
+        <v>49.54</v>
       </c>
       <c r="E254">
-        <v>1488.56</v>
+        <v>990.45</v>
       </c>
       <c r="F254">
-        <v>1543.78</v>
+        <v>949.73</v>
       </c>
       <c r="G254">
-        <v>1540.37</v>
+        <v>936.1</v>
       </c>
       <c r="H254">
-        <v>1629.3</v>
+        <v>1006.05</v>
       </c>
       <c r="I254">
-        <v>91972</v>
+        <v>915803</v>
       </c>
       <c r="J254">
-        <v>260139</v>
+        <v>2623676</v>
       </c>
       <c r="K254">
         <v>0.35</v>
@@ -23042,22 +23039,22 @@
         <v>118</v>
       </c>
       <c r="N254">
-        <v>1557.08</v>
+        <v>1024.66</v>
       </c>
       <c r="O254">
-        <v>53.25</v>
+        <v>34.22</v>
       </c>
       <c r="P254">
-        <v>1378.22</v>
+        <v>931.27</v>
       </c>
       <c r="Q254">
-        <v>1617.86</v>
+        <v>1085.26</v>
       </c>
       <c r="R254">
-        <v>5.48</v>
+        <v>5.22</v>
       </c>
       <c r="S254">
-        <v>10.96</v>
+        <v>10.45</v>
       </c>
       <c r="T254" t="s">
         <v>155</v>
@@ -23069,7 +23066,7 @@
         <v>593</v>
       </c>
       <c r="W254" t="s">
-        <v>128</v>
+        <v>596</v>
       </c>
     </row>
     <row r="255" spans="1:23">
